--- a/platform_PiN_output/Afghanistan___AFG/PiN_results_Afghanistan___AFG_0925_10AM.xlsx
+++ b/platform_PiN_output/Afghanistan___AFG/PiN_results_Afghanistan___AFG_0925_10AM.xlsx
@@ -780,16 +780,16 @@
         <v>10356964</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>24.4</v>
+        <v>24</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>4312446</v>
+        <v>4232192</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>341038</v>
+        <v>421291</v>
       </c>
       <c r="Q6" s="9" t="n">
         <v>14.9</v>
@@ -842,16 +842,16 @@
         <v>3155455</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="N7" s="11" t="n">
-        <v>651843</v>
+        <v>646401</v>
       </c>
       <c r="O7" s="11" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="P7" s="11" t="n">
-        <v>56288</v>
+        <v>61730</v>
       </c>
       <c r="Q7" s="11" t="n">
         <v>14.7</v>
@@ -904,16 +904,16 @@
         <v>7201509</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>27.9</v>
+        <v>27.3</v>
       </c>
       <c r="N8" s="11" t="n">
-        <v>3660604</v>
+        <v>3585791</v>
       </c>
       <c r="O8" s="11" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="P8" s="11" t="n">
-        <v>284749</v>
+        <v>359562</v>
       </c>
       <c r="Q8" s="11" t="n">
         <v>15</v>
@@ -1336,16 +1336,16 @@
         <v>158111</v>
       </c>
       <c r="I9" s="24" t="n">
-        <v>13.4</v>
+        <v>12.9</v>
       </c>
       <c r="J9" s="24" t="n">
-        <v>28148</v>
+        <v>27090</v>
       </c>
       <c r="K9" s="25" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="L9" s="25" t="n">
-        <v>3245</v>
+        <v>4302</v>
       </c>
       <c r="M9" s="26" t="n">
         <v>9.699999999999999</v>
@@ -1532,16 +1532,16 @@
         <v>14096</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>18.1</v>
+        <v>17.6</v>
       </c>
       <c r="J13" s="24" t="n">
-        <v>4060</v>
+        <v>3947</v>
       </c>
       <c r="K13" s="25" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L13" s="25" t="n">
-        <v>338</v>
+        <v>451</v>
       </c>
       <c r="M13" s="26" t="n">
         <v>17.6</v>
@@ -1581,16 +1581,16 @@
         <v>5356</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>16.9</v>
+        <v>16.5</v>
       </c>
       <c r="J14" s="24" t="n">
-        <v>1393</v>
+        <v>1362</v>
       </c>
       <c r="K14" s="25" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="L14" s="25" t="n">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="M14" s="26" t="n">
         <v>17.3</v>
@@ -1679,16 +1679,16 @@
         <v>4166</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>34.5</v>
+        <v>34.1</v>
       </c>
       <c r="J16" s="24" t="n">
-        <v>2850</v>
+        <v>2819</v>
       </c>
       <c r="K16" s="25" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="L16" s="25" t="n">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="M16" s="26" t="n">
         <v>13.3</v>
@@ -1973,16 +1973,16 @@
         <v>19468</v>
       </c>
       <c r="I22" s="24" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="J22" s="24" t="n">
-        <v>3729</v>
+        <v>3580</v>
       </c>
       <c r="K22" s="25" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L22" s="25" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="M22" s="26" t="n">
         <v>22.3</v>
@@ -2169,16 +2169,16 @@
         <v>32253</v>
       </c>
       <c r="I26" s="24" t="n">
-        <v>23.5</v>
+        <v>22.2</v>
       </c>
       <c r="J26" s="24" t="n">
-        <v>11515</v>
+        <v>10891</v>
       </c>
       <c r="K26" s="25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="L26" s="25" t="n">
-        <v>0</v>
+        <v>625</v>
       </c>
       <c r="M26" s="26" t="n">
         <v>10.7</v>
@@ -2218,16 +2218,16 @@
         <v>10464</v>
       </c>
       <c r="I27" s="24" t="n">
-        <v>25.3</v>
+        <v>24.9</v>
       </c>
       <c r="J27" s="24" t="n">
-        <v>4812</v>
+        <v>4733</v>
       </c>
       <c r="K27" s="25" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="L27" s="25" t="n">
-        <v>321</v>
+        <v>399</v>
       </c>
       <c r="M27" s="26" t="n">
         <v>18</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Q27" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2365,16 +2365,16 @@
         <v>12119</v>
       </c>
       <c r="I30" s="24" t="n">
-        <v>33</v>
+        <v>31.1</v>
       </c>
       <c r="J30" s="24" t="n">
-        <v>8101</v>
+        <v>7650</v>
       </c>
       <c r="K30" s="25" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="L30" s="25" t="n">
-        <v>225</v>
+        <v>675</v>
       </c>
       <c r="M30" s="26" t="n">
         <v>16.8</v>
@@ -2708,16 +2708,16 @@
         <v>7798</v>
       </c>
       <c r="I37" s="24" t="n">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
       <c r="J37" s="24" t="n">
-        <v>1535</v>
+        <v>1493</v>
       </c>
       <c r="K37" s="25" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="L37" s="25" t="n">
-        <v>581</v>
+        <v>622</v>
       </c>
       <c r="M37" s="26" t="n">
         <v>14.6</v>
@@ -3198,16 +3198,16 @@
         <v>49870</v>
       </c>
       <c r="I47" s="24" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="J47" s="24" t="n">
-        <v>18000</v>
+        <v>17721</v>
       </c>
       <c r="K47" s="25" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L47" s="25" t="n">
-        <v>9</v>
+        <v>287</v>
       </c>
       <c r="M47" s="26" t="n">
         <v>8.699999999999999</v>
@@ -3296,16 +3296,16 @@
         <v>16720</v>
       </c>
       <c r="I49" s="24" t="n">
-        <v>15.9</v>
+        <v>15</v>
       </c>
       <c r="J49" s="24" t="n">
-        <v>3612</v>
+        <v>3406</v>
       </c>
       <c r="K49" s="25" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="L49" s="25" t="n">
-        <v>206</v>
+        <v>413</v>
       </c>
       <c r="M49" s="26" t="n">
         <v>9.5</v>
@@ -3394,16 +3394,16 @@
         <v>34028</v>
       </c>
       <c r="I51" s="24" t="n">
-        <v>20.2</v>
+        <v>18.5</v>
       </c>
       <c r="J51" s="24" t="n">
-        <v>9650</v>
+        <v>8869</v>
       </c>
       <c r="K51" s="25" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="L51" s="25" t="n">
-        <v>206</v>
+        <v>988</v>
       </c>
       <c r="M51" s="26" t="n">
         <v>8.300000000000001</v>
@@ -3492,16 +3492,16 @@
         <v>12528</v>
       </c>
       <c r="I53" s="24" t="n">
-        <v>16.9</v>
+        <v>15.5</v>
       </c>
       <c r="J53" s="24" t="n">
-        <v>2848</v>
+        <v>2614</v>
       </c>
       <c r="K53" s="25" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="L53" s="25" t="n">
-        <v>85</v>
+        <v>318</v>
       </c>
       <c r="M53" s="26" t="n">
         <v>8.4</v>
@@ -3593,13 +3593,13 @@
         <v>18.1</v>
       </c>
       <c r="J55" s="24" t="n">
-        <v>22199</v>
+        <v>22193</v>
       </c>
       <c r="K55" s="25" t="n">
         <v>4.4</v>
       </c>
       <c r="L55" s="25" t="n">
-        <v>5420</v>
+        <v>5427</v>
       </c>
       <c r="M55" s="26" t="n">
         <v>15.4</v>
@@ -3639,16 +3639,16 @@
         <v>68668</v>
       </c>
       <c r="I56" s="24" t="n">
-        <v>36.7</v>
+        <v>36.1</v>
       </c>
       <c r="J56" s="24" t="n">
-        <v>58175</v>
+        <v>57308</v>
       </c>
       <c r="K56" s="25" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="L56" s="25" t="n">
-        <v>5687</v>
+        <v>6554</v>
       </c>
       <c r="M56" s="26" t="n">
         <v>16.4</v>
@@ -3691,13 +3691,13 @@
         <v>13</v>
       </c>
       <c r="J57" s="24" t="n">
-        <v>11103</v>
+        <v>11069</v>
       </c>
       <c r="K57" s="25" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="L57" s="25" t="n">
-        <v>1890</v>
+        <v>1924</v>
       </c>
       <c r="M57" s="26" t="n">
         <v>9.300000000000001</v>
@@ -3737,16 +3737,16 @@
         <v>38149</v>
       </c>
       <c r="I58" s="24" t="n">
-        <v>22.3</v>
+        <v>21.4</v>
       </c>
       <c r="J58" s="24" t="n">
-        <v>14810</v>
+        <v>14216</v>
       </c>
       <c r="K58" s="25" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="L58" s="25" t="n">
-        <v>3218</v>
+        <v>3812</v>
       </c>
       <c r="M58" s="26" t="n">
         <v>15.6</v>
@@ -3835,16 +3835,16 @@
         <v>40544</v>
       </c>
       <c r="I60" s="24" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="J60" s="24" t="n">
-        <v>17348</v>
+        <v>17172</v>
       </c>
       <c r="K60" s="25" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="L60" s="25" t="n">
-        <v>1237</v>
+        <v>1414</v>
       </c>
       <c r="M60" s="26" t="n">
         <v>14.3</v>
@@ -3884,16 +3884,16 @@
         <v>74918</v>
       </c>
       <c r="I61" s="24" t="n">
-        <v>27.7</v>
+        <v>27.4</v>
       </c>
       <c r="J61" s="24" t="n">
-        <v>35926</v>
+        <v>35488</v>
       </c>
       <c r="K61" s="25" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="L61" s="25" t="n">
-        <v>2629</v>
+        <v>3067</v>
       </c>
       <c r="M61" s="26" t="n">
         <v>12.5</v>
@@ -3933,16 +3933,16 @@
         <v>31688</v>
       </c>
       <c r="I62" s="24" t="n">
-        <v>43.1</v>
+        <v>42.6</v>
       </c>
       <c r="J62" s="24" t="n">
-        <v>34921</v>
+        <v>34534</v>
       </c>
       <c r="K62" s="25" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="L62" s="25" t="n">
-        <v>2569</v>
+        <v>2955</v>
       </c>
       <c r="M62" s="26" t="n">
         <v>14.6</v>
@@ -3982,16 +3982,16 @@
         <v>15996</v>
       </c>
       <c r="I63" s="24" t="n">
-        <v>31</v>
+        <v>30.1</v>
       </c>
       <c r="J63" s="24" t="n">
-        <v>10488</v>
+        <v>10187</v>
       </c>
       <c r="K63" s="25" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="L63" s="25" t="n">
-        <v>834</v>
+        <v>1135</v>
       </c>
       <c r="M63" s="26" t="n">
         <v>19.2</v>
@@ -4080,16 +4080,16 @@
         <v>13601</v>
       </c>
       <c r="I65" s="24" t="n">
-        <v>37.1</v>
+        <v>35.6</v>
       </c>
       <c r="J65" s="24" t="n">
-        <v>12903</v>
+        <v>12374</v>
       </c>
       <c r="K65" s="25" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="L65" s="25" t="n">
-        <v>1621</v>
+        <v>2150</v>
       </c>
       <c r="M65" s="26" t="n">
         <v>19.1</v>
@@ -4129,16 +4129,16 @@
         <v>26556</v>
       </c>
       <c r="I66" s="24" t="n">
-        <v>23.7</v>
+        <v>23.1</v>
       </c>
       <c r="J66" s="24" t="n">
-        <v>10584</v>
+        <v>10304</v>
       </c>
       <c r="K66" s="25" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="L66" s="25" t="n">
-        <v>735</v>
+        <v>1015</v>
       </c>
       <c r="M66" s="26" t="n">
         <v>15.2</v>
@@ -4178,16 +4178,16 @@
         <v>12226</v>
       </c>
       <c r="I67" s="24" t="n">
-        <v>46.9</v>
+        <v>46.7</v>
       </c>
       <c r="J67" s="24" t="n">
-        <v>18120</v>
+        <v>18012</v>
       </c>
       <c r="K67" s="25" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="L67" s="25" t="n">
-        <v>2811</v>
+        <v>2919</v>
       </c>
       <c r="M67" s="26" t="n">
         <v>14.1</v>
@@ -4227,16 +4227,16 @@
         <v>19448</v>
       </c>
       <c r="I68" s="24" t="n">
-        <v>62.5</v>
+        <v>61</v>
       </c>
       <c r="J68" s="24" t="n">
-        <v>56695</v>
+        <v>55326</v>
       </c>
       <c r="K68" s="25" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="L68" s="25" t="n">
-        <v>2190</v>
+        <v>3559</v>
       </c>
       <c r="M68" s="26" t="n">
         <v>13.6</v>
@@ -4276,16 +4276,16 @@
         <v>40962</v>
       </c>
       <c r="I69" s="24" t="n">
-        <v>23.1</v>
+        <v>22</v>
       </c>
       <c r="J69" s="24" t="n">
-        <v>16520</v>
+        <v>15730</v>
       </c>
       <c r="K69" s="25" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="L69" s="25" t="n">
-        <v>2953</v>
+        <v>3743</v>
       </c>
       <c r="M69" s="26" t="n">
         <v>15.4</v>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="Q69" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -4325,16 +4325,16 @@
         <v>28314</v>
       </c>
       <c r="I70" s="24" t="n">
-        <v>27.7</v>
+        <v>27.5</v>
       </c>
       <c r="J70" s="24" t="n">
-        <v>14821</v>
+        <v>14684</v>
       </c>
       <c r="K70" s="25" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="L70" s="25" t="n">
-        <v>1543</v>
+        <v>1679</v>
       </c>
       <c r="M70" s="26" t="n">
         <v>16.5</v>
@@ -4374,16 +4374,16 @@
         <v>9309</v>
       </c>
       <c r="I71" s="24" t="n">
-        <v>44.1</v>
+        <v>42.6</v>
       </c>
       <c r="J71" s="24" t="n">
-        <v>11402</v>
+        <v>11025</v>
       </c>
       <c r="K71" s="25" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="L71" s="25" t="n">
-        <v>829</v>
+        <v>1206</v>
       </c>
       <c r="M71" s="26" t="n">
         <v>16.7</v>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="Q71" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -4472,16 +4472,16 @@
         <v>11174</v>
       </c>
       <c r="I73" s="24" t="n">
-        <v>28.7</v>
+        <v>27.9</v>
       </c>
       <c r="J73" s="24" t="n">
-        <v>6282</v>
+        <v>6094</v>
       </c>
       <c r="K73" s="25" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="L73" s="25" t="n">
-        <v>438</v>
+        <v>625</v>
       </c>
       <c r="M73" s="26" t="n">
         <v>18.1</v>
@@ -4521,16 +4521,16 @@
         <v>8318</v>
       </c>
       <c r="I74" s="24" t="n">
-        <v>56.2</v>
+        <v>51.2</v>
       </c>
       <c r="J74" s="24" t="n">
-        <v>20539</v>
+        <v>18727</v>
       </c>
       <c r="K74" s="25" t="n">
-        <v>4.1</v>
+        <v>9</v>
       </c>
       <c r="L74" s="25" t="n">
-        <v>1493</v>
+        <v>3306</v>
       </c>
       <c r="M74" s="26" t="n">
         <v>17</v>
@@ -4570,16 +4570,16 @@
         <v>8942</v>
       </c>
       <c r="I75" s="24" t="n">
-        <v>34.8</v>
+        <v>34.5</v>
       </c>
       <c r="J75" s="24" t="n">
-        <v>7552</v>
+        <v>7481</v>
       </c>
       <c r="K75" s="25" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="L75" s="25" t="n">
-        <v>1490</v>
+        <v>1561</v>
       </c>
       <c r="M75" s="26" t="n">
         <v>17.1</v>
@@ -4668,16 +4668,16 @@
         <v>63057</v>
       </c>
       <c r="I77" s="24" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="J77" s="24" t="n">
-        <v>8128</v>
+        <v>7603</v>
       </c>
       <c r="K77" s="25" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="L77" s="25" t="n">
-        <v>185</v>
+        <v>710</v>
       </c>
       <c r="M77" s="26" t="n">
         <v>19.7</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="Q77" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -4717,16 +4717,16 @@
         <v>39796</v>
       </c>
       <c r="I78" s="24" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="J78" s="24" t="n">
-        <v>8013</v>
+        <v>7886</v>
       </c>
       <c r="K78" s="25" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L78" s="25" t="n">
-        <v>9</v>
+        <v>136</v>
       </c>
       <c r="M78" s="26" t="n">
         <v>14.7</v>
@@ -4815,16 +4815,16 @@
         <v>25434</v>
       </c>
       <c r="I80" s="24" t="n">
-        <v>22.5</v>
+        <v>20.8</v>
       </c>
       <c r="J80" s="24" t="n">
-        <v>8611</v>
+        <v>7964</v>
       </c>
       <c r="K80" s="25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="L80" s="25" t="n">
-        <v>0</v>
+        <v>647</v>
       </c>
       <c r="M80" s="26" t="n">
         <v>11.1</v>
@@ -5158,16 +5158,16 @@
         <v>8592</v>
       </c>
       <c r="I87" s="24" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J87" s="24" t="n">
-        <v>263</v>
+        <v>234</v>
       </c>
       <c r="K87" s="25" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="L87" s="25" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="M87" s="26" t="n">
         <v>5.3</v>
@@ -6481,16 +6481,16 @@
         <v>13024</v>
       </c>
       <c r="I114" s="24" t="n">
-        <v>37.6</v>
+        <v>35.7</v>
       </c>
       <c r="J114" s="24" t="n">
-        <v>10545</v>
+        <v>10018</v>
       </c>
       <c r="K114" s="25" t="n">
-        <v>5.2</v>
+        <v>7.1</v>
       </c>
       <c r="L114" s="25" t="n">
-        <v>1457</v>
+        <v>1984</v>
       </c>
       <c r="M114" s="26" t="n">
         <v>10.8</v>
@@ -6628,16 +6628,16 @@
         <v>4471</v>
       </c>
       <c r="I117" s="24" t="n">
-        <v>36.1</v>
+        <v>35</v>
       </c>
       <c r="J117" s="24" t="n">
-        <v>3430</v>
+        <v>3322</v>
       </c>
       <c r="K117" s="25" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="L117" s="25" t="n">
-        <v>539</v>
+        <v>646</v>
       </c>
       <c r="M117" s="26" t="n">
         <v>11.1</v>
@@ -6824,16 +6824,16 @@
         <v>9248</v>
       </c>
       <c r="I121" s="24" t="n">
-        <v>30.1</v>
+        <v>29.8</v>
       </c>
       <c r="J121" s="24" t="n">
-        <v>5287</v>
+        <v>5228</v>
       </c>
       <c r="K121" s="25" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="L121" s="25" t="n">
-        <v>471</v>
+        <v>530</v>
       </c>
       <c r="M121" s="26" t="n">
         <v>14.5</v>
@@ -7363,16 +7363,16 @@
         <v>5310</v>
       </c>
       <c r="I132" s="24" t="n">
-        <v>36.1</v>
+        <v>34.7</v>
       </c>
       <c r="J132" s="24" t="n">
-        <v>3892</v>
+        <v>3744</v>
       </c>
       <c r="K132" s="25" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="L132" s="25" t="n">
-        <v>119</v>
+        <v>267</v>
       </c>
       <c r="M132" s="26" t="n">
         <v>13.6</v>
@@ -7412,16 +7412,16 @@
         <v>2613</v>
       </c>
       <c r="I133" s="24" t="n">
-        <v>44.3</v>
+        <v>43.8</v>
       </c>
       <c r="J133" s="24" t="n">
-        <v>2744</v>
+        <v>2711</v>
       </c>
       <c r="K133" s="25" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="L133" s="25" t="n">
-        <v>115</v>
+        <v>148</v>
       </c>
       <c r="M133" s="26" t="n">
         <v>11.7</v>
@@ -7657,16 +7657,16 @@
         <v>3843</v>
       </c>
       <c r="I138" s="24" t="n">
-        <v>46</v>
+        <v>45.7</v>
       </c>
       <c r="J138" s="24" t="n">
-        <v>4764</v>
+        <v>4732</v>
       </c>
       <c r="K138" s="25" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="L138" s="25" t="n">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="M138" s="26" t="n">
         <v>15</v>
@@ -7804,16 +7804,16 @@
         <v>3957</v>
       </c>
       <c r="I141" s="24" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
       <c r="J141" s="24" t="n">
-        <v>674</v>
+        <v>659</v>
       </c>
       <c r="K141" s="25" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="L141" s="25" t="n">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="M141" s="26" t="n">
         <v>8.699999999999999</v>
@@ -7853,16 +7853,16 @@
         <v>463</v>
       </c>
       <c r="I142" s="24" t="n">
-        <v>72.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="J142" s="24" t="n">
-        <v>11397</v>
+        <v>11339</v>
       </c>
       <c r="K142" s="25" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="L142" s="25" t="n">
-        <v>1621</v>
+        <v>1679</v>
       </c>
       <c r="M142" s="26" t="n">
         <v>14.1</v>
@@ -7902,16 +7902,16 @@
         <v>2253</v>
       </c>
       <c r="I143" s="24" t="n">
-        <v>57.2</v>
+        <v>55.8</v>
       </c>
       <c r="J143" s="24" t="n">
-        <v>4186</v>
+        <v>4079</v>
       </c>
       <c r="K143" s="25" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="L143" s="25" t="n">
-        <v>43</v>
+        <v>150</v>
       </c>
       <c r="M143" s="26" t="n">
         <v>11.4</v>
@@ -8000,16 +8000,16 @@
         <v>2905</v>
       </c>
       <c r="I145" s="24" t="n">
-        <v>57.3</v>
+        <v>56.9</v>
       </c>
       <c r="J145" s="24" t="n">
-        <v>7662</v>
+        <v>7612</v>
       </c>
       <c r="K145" s="25" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="L145" s="25" t="n">
-        <v>801</v>
+        <v>851</v>
       </c>
       <c r="M145" s="26" t="n">
         <v>15</v>
@@ -8147,16 +8147,16 @@
         <v>55157</v>
       </c>
       <c r="I148" s="24" t="n">
-        <v>22.8</v>
+        <v>22.5</v>
       </c>
       <c r="J148" s="24" t="n">
-        <v>21659</v>
+        <v>21398</v>
       </c>
       <c r="K148" s="25" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="L148" s="25" t="n">
-        <v>2165</v>
+        <v>2426</v>
       </c>
       <c r="M148" s="26" t="n">
         <v>16.8</v>
@@ -8245,16 +8245,16 @@
         <v>28465</v>
       </c>
       <c r="I150" s="24" t="n">
-        <v>37</v>
+        <v>32.7</v>
       </c>
       <c r="J150" s="24" t="n">
-        <v>22316</v>
+        <v>19732</v>
       </c>
       <c r="K150" s="25" t="n">
-        <v>3.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L150" s="25" t="n">
-        <v>2375</v>
+        <v>4960</v>
       </c>
       <c r="M150" s="26" t="n">
         <v>11.9</v>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="Q150" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -8294,16 +8294,16 @@
         <v>2150</v>
       </c>
       <c r="I151" s="24" t="n">
-        <v>53.2</v>
+        <v>52.9</v>
       </c>
       <c r="J151" s="24" t="n">
-        <v>3863</v>
+        <v>3842</v>
       </c>
       <c r="K151" s="25" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="L151" s="25" t="n">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="M151" s="26" t="n">
         <v>13.8</v>
@@ -8539,16 +8539,16 @@
         <v>3077</v>
       </c>
       <c r="I156" s="24" t="n">
-        <v>74.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="J156" s="24" t="n">
-        <v>19909</v>
+        <v>18310</v>
       </c>
       <c r="K156" s="25" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L156" s="25" t="n">
-        <v>799</v>
+        <v>2398</v>
       </c>
       <c r="M156" s="26" t="n">
         <v>10.9</v>
@@ -8686,16 +8686,16 @@
         <v>46627</v>
       </c>
       <c r="I159" s="24" t="n">
-        <v>57.3</v>
+        <v>55.3</v>
       </c>
       <c r="J159" s="24" t="n">
-        <v>72907</v>
+        <v>70358</v>
       </c>
       <c r="K159" s="25" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="L159" s="25" t="n">
-        <v>202</v>
+        <v>2752</v>
       </c>
       <c r="M159" s="26" t="n">
         <v>5.8</v>
@@ -8735,16 +8735,16 @@
         <v>34047</v>
       </c>
       <c r="I160" s="24" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J160" s="24" t="n">
-        <v>11423</v>
+        <v>8442</v>
       </c>
       <c r="K160" s="25" t="n">
-        <v>0.8</v>
+        <v>6.8</v>
       </c>
       <c r="L160" s="25" t="n">
-        <v>402</v>
+        <v>3383</v>
       </c>
       <c r="M160" s="26" t="n">
         <v>7.6</v>
@@ -8784,16 +8784,16 @@
         <v>17047</v>
       </c>
       <c r="I161" s="24" t="n">
-        <v>30</v>
+        <v>19.4</v>
       </c>
       <c r="J161" s="24" t="n">
-        <v>9533</v>
+        <v>6184</v>
       </c>
       <c r="K161" s="25" t="n">
-        <v>0.4</v>
+        <v>11</v>
       </c>
       <c r="L161" s="25" t="n">
-        <v>139</v>
+        <v>3489</v>
       </c>
       <c r="M161" s="26" t="n">
         <v>16</v>
@@ -8809,7 +8809,7 @@
       </c>
       <c r="Q161" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -8833,16 +8833,16 @@
         <v>6471</v>
       </c>
       <c r="I162" s="24" t="n">
-        <v>82.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J162" s="24" t="n">
-        <v>33670</v>
+        <v>33551</v>
       </c>
       <c r="K162" s="25" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="L162" s="25" t="n">
-        <v>238</v>
+        <v>357</v>
       </c>
       <c r="M162" s="26" t="n">
         <v>0.9</v>
@@ -8882,16 +8882,16 @@
         <v>4753</v>
       </c>
       <c r="I163" s="24" t="n">
-        <v>66</v>
+        <v>65.8</v>
       </c>
       <c r="J163" s="24" t="n">
-        <v>20191</v>
+        <v>20108</v>
       </c>
       <c r="K163" s="25" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="L163" s="25" t="n">
-        <v>331</v>
+        <v>413</v>
       </c>
       <c r="M163" s="26" t="n">
         <v>17.4</v>
@@ -8931,16 +8931,16 @@
         <v>17991</v>
       </c>
       <c r="I164" s="24" t="n">
-        <v>27.1</v>
+        <v>26.1</v>
       </c>
       <c r="J164" s="24" t="n">
-        <v>8357</v>
+        <v>8044</v>
       </c>
       <c r="K164" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L164" s="25" t="n">
-        <v>313</v>
+        <v>627</v>
       </c>
       <c r="M164" s="26" t="n">
         <v>13.6</v>
@@ -9078,16 +9078,16 @@
         <v>18658</v>
       </c>
       <c r="I167" s="24" t="n">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J167" s="24" t="n">
-        <v>1938</v>
+        <v>1858</v>
       </c>
       <c r="K167" s="25" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L167" s="25" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M167" s="26" t="n">
         <v>7.9</v>
@@ -9127,16 +9127,16 @@
         <v>67</v>
       </c>
       <c r="I168" s="24" t="n">
-        <v>85.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="J168" s="24" t="n">
-        <v>5881</v>
+        <v>5547</v>
       </c>
       <c r="K168" s="25" t="n">
-        <v>2</v>
+        <v>6.8</v>
       </c>
       <c r="L168" s="25" t="n">
-        <v>134</v>
+        <v>468</v>
       </c>
       <c r="M168" s="26" t="n">
         <v>11.2</v>
@@ -9176,16 +9176,16 @@
         <v>19761</v>
       </c>
       <c r="I169" s="24" t="n">
-        <v>35.1</v>
+        <v>29.8</v>
       </c>
       <c r="J169" s="24" t="n">
-        <v>13039</v>
+        <v>11083</v>
       </c>
       <c r="K169" s="25" t="n">
-        <v>0.8</v>
+        <v>6.1</v>
       </c>
       <c r="L169" s="25" t="n">
-        <v>301</v>
+        <v>2257</v>
       </c>
       <c r="M169" s="26" t="n">
         <v>11</v>
@@ -9225,16 +9225,16 @@
         <v>2896</v>
       </c>
       <c r="I170" s="24" t="n">
-        <v>43.3</v>
+        <v>40.4</v>
       </c>
       <c r="J170" s="24" t="n">
-        <v>4623</v>
+        <v>4314</v>
       </c>
       <c r="K170" s="25" t="n">
-        <v>2.9</v>
+        <v>5.8</v>
       </c>
       <c r="L170" s="25" t="n">
-        <v>309</v>
+        <v>618</v>
       </c>
       <c r="M170" s="26" t="n">
         <v>26.7</v>
@@ -9274,16 +9274,16 @@
         <v>20025</v>
       </c>
       <c r="I171" s="24" t="n">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J171" s="24" t="n">
-        <v>2099</v>
+        <v>2012</v>
       </c>
       <c r="K171" s="25" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L171" s="25" t="n">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="M171" s="26" t="n">
         <v>8.4</v>
@@ -9421,16 +9421,16 @@
         <v>6250</v>
       </c>
       <c r="I174" s="24" t="n">
-        <v>62.2</v>
+        <v>61.4</v>
       </c>
       <c r="J174" s="24" t="n">
-        <v>23552</v>
+        <v>23255</v>
       </c>
       <c r="K174" s="25" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="L174" s="25" t="n">
-        <v>3274</v>
+        <v>3572</v>
       </c>
       <c r="M174" s="26" t="n">
         <v>12.6</v>
@@ -9568,16 +9568,16 @@
         <v>25173</v>
       </c>
       <c r="I177" s="24" t="n">
-        <v>34.8</v>
+        <v>34.5</v>
       </c>
       <c r="J177" s="24" t="n">
-        <v>17431</v>
+        <v>17270</v>
       </c>
       <c r="K177" s="25" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="L177" s="25" t="n">
-        <v>322</v>
+        <v>483</v>
       </c>
       <c r="M177" s="26" t="n">
         <v>14.3</v>
@@ -9715,16 +9715,16 @@
         <v>26089</v>
       </c>
       <c r="I180" s="24" t="n">
-        <v>25.2</v>
+        <v>24.7</v>
       </c>
       <c r="J180" s="24" t="n">
-        <v>10750</v>
+        <v>10511</v>
       </c>
       <c r="K180" s="25" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="L180" s="25" t="n">
-        <v>1553</v>
+        <v>1792</v>
       </c>
       <c r="M180" s="26" t="n">
         <v>9.9</v>
@@ -9911,16 +9911,16 @@
         <v>20795</v>
       </c>
       <c r="I184" s="24" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="J184" s="24" t="n">
-        <v>8383</v>
+        <v>8274</v>
       </c>
       <c r="K184" s="25" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="L184" s="25" t="n">
-        <v>544</v>
+        <v>653</v>
       </c>
       <c r="M184" s="26" t="n">
         <v>13.6</v>
@@ -11185,16 +11185,16 @@
         <v>8851</v>
       </c>
       <c r="I210" s="24" t="n">
-        <v>17.1</v>
+        <v>16.2</v>
       </c>
       <c r="J210" s="24" t="n">
-        <v>2385</v>
+        <v>2260</v>
       </c>
       <c r="K210" s="25" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="L210" s="25" t="n">
-        <v>126</v>
+        <v>251</v>
       </c>
       <c r="M210" s="26" t="n">
         <v>18.5</v>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="Q210" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -11822,16 +11822,16 @@
         <v>108527</v>
       </c>
       <c r="I223" s="24" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="J223" s="24" t="n">
-        <v>42008</v>
+        <v>41394</v>
       </c>
       <c r="K223" s="25" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="L223" s="25" t="n">
-        <v>3030</v>
+        <v>3644</v>
       </c>
       <c r="M223" s="26" t="n">
         <v>16</v>
@@ -12851,16 +12851,16 @@
         <v>71896</v>
       </c>
       <c r="I244" s="24" t="n">
-        <v>27.4</v>
+        <v>27</v>
       </c>
       <c r="J244" s="24" t="n">
-        <v>35638</v>
+        <v>35139</v>
       </c>
       <c r="K244" s="25" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="L244" s="25" t="n">
-        <v>1495</v>
+        <v>1993</v>
       </c>
       <c r="M244" s="26" t="n">
         <v>16.1</v>
@@ -13096,16 +13096,16 @@
         <v>14379</v>
       </c>
       <c r="I249" s="24" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J249" s="24" t="n">
-        <v>1657</v>
+        <v>1502</v>
       </c>
       <c r="K249" s="25" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="L249" s="25" t="n">
-        <v>1010</v>
+        <v>1166</v>
       </c>
       <c r="M249" s="26" t="n">
         <v>15.8</v>
@@ -13145,16 +13145,16 @@
         <v>4612</v>
       </c>
       <c r="I250" s="24" t="n">
-        <v>22</v>
+        <v>21.6</v>
       </c>
       <c r="J250" s="24" t="n">
-        <v>1600</v>
+        <v>1569</v>
       </c>
       <c r="K250" s="25" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="L250" s="25" t="n">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="M250" s="26" t="n">
         <v>12.4</v>
@@ -13194,16 +13194,16 @@
         <v>16443</v>
       </c>
       <c r="I251" s="24" t="n">
-        <v>18.6</v>
+        <v>17.4</v>
       </c>
       <c r="J251" s="24" t="n">
-        <v>5103</v>
+        <v>4763</v>
       </c>
       <c r="K251" s="25" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="L251" s="25" t="n">
-        <v>1474</v>
+        <v>1814</v>
       </c>
       <c r="M251" s="26" t="n">
         <v>16.1</v>
@@ -13390,16 +13390,16 @@
         <v>98027</v>
       </c>
       <c r="I255" s="24" t="n">
-        <v>13.2</v>
+        <v>12.3</v>
       </c>
       <c r="J255" s="24" t="n">
-        <v>20411</v>
+        <v>19016</v>
       </c>
       <c r="K255" s="25" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="L255" s="25" t="n">
-        <v>7091</v>
+        <v>8485</v>
       </c>
       <c r="M255" s="26" t="n">
         <v>18.7</v>
@@ -13733,16 +13733,16 @@
         <v>32497</v>
       </c>
       <c r="I262" s="24" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="J262" s="24" t="n">
-        <v>5209</v>
+        <v>5021</v>
       </c>
       <c r="K262" s="25" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="L262" s="25" t="n">
-        <v>214</v>
+        <v>402</v>
       </c>
       <c r="M262" s="26" t="n">
         <v>19.3</v>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="Q262" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -14027,16 +14027,16 @@
         <v>27642</v>
       </c>
       <c r="I268" s="24" t="n">
-        <v>22.3</v>
+        <v>21.9</v>
       </c>
       <c r="J268" s="24" t="n">
-        <v>10501</v>
+        <v>10288</v>
       </c>
       <c r="K268" s="25" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="L268" s="25" t="n">
-        <v>1699</v>
+        <v>1912</v>
       </c>
       <c r="M268" s="26" t="n">
         <v>15.3</v>
@@ -14213,16 +14213,16 @@
         <v>18125</v>
       </c>
       <c r="I272" s="24" t="n">
-        <v>38.9</v>
+        <v>37.5</v>
       </c>
       <c r="J272" s="24" t="n">
-        <v>26181</v>
+        <v>25294</v>
       </c>
       <c r="K272" s="25" t="n">
-        <v>15</v>
+        <v>16.3</v>
       </c>
       <c r="L272" s="25" t="n">
-        <v>10121</v>
+        <v>11008</v>
       </c>
       <c r="M272" s="26" t="n">
         <v>19.2</v>
@@ -14458,16 +14458,16 @@
         <v>59628</v>
       </c>
       <c r="I277" s="24" t="n">
-        <v>20.9</v>
+        <v>20.5</v>
       </c>
       <c r="J277" s="24" t="n">
-        <v>20129</v>
+        <v>19722</v>
       </c>
       <c r="K277" s="25" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="L277" s="25" t="n">
-        <v>5295</v>
+        <v>5702</v>
       </c>
       <c r="M277" s="26" t="n">
         <v>11.7</v>
@@ -14654,16 +14654,16 @@
         <v>22057</v>
       </c>
       <c r="I281" s="24" t="n">
-        <v>39.2</v>
+        <v>38.7</v>
       </c>
       <c r="J281" s="24" t="n">
-        <v>19757</v>
+        <v>19508</v>
       </c>
       <c r="K281" s="25" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="L281" s="25" t="n">
-        <v>1871</v>
+        <v>2120</v>
       </c>
       <c r="M281" s="26" t="n">
         <v>13.4</v>
@@ -14801,16 +14801,16 @@
         <v>20787</v>
       </c>
       <c r="I284" s="24" t="n">
-        <v>31.4</v>
+        <v>29.7</v>
       </c>
       <c r="J284" s="24" t="n">
-        <v>12314</v>
+        <v>11649</v>
       </c>
       <c r="K284" s="25" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="L284" s="25" t="n">
-        <v>166</v>
+        <v>831</v>
       </c>
       <c r="M284" s="26" t="n">
         <v>15.3</v>
@@ -15487,16 +15487,16 @@
         <v>8196</v>
       </c>
       <c r="I298" s="24" t="n">
-        <v>23.7</v>
+        <v>22.4</v>
       </c>
       <c r="J298" s="24" t="n">
-        <v>3342</v>
+        <v>3158</v>
       </c>
       <c r="K298" s="25" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="L298" s="25" t="n">
-        <v>583</v>
+        <v>767</v>
       </c>
       <c r="M298" s="26" t="n">
         <v>13.9</v>
@@ -15585,16 +15585,16 @@
         <v>12037</v>
       </c>
       <c r="I300" s="24" t="n">
-        <v>47.5</v>
+        <v>29.1</v>
       </c>
       <c r="J300" s="24" t="n">
-        <v>15560</v>
+        <v>9542</v>
       </c>
       <c r="K300" s="25" t="n">
-        <v>8.1</v>
+        <v>26.5</v>
       </c>
       <c r="L300" s="25" t="n">
-        <v>2642</v>
+        <v>8661</v>
       </c>
       <c r="M300" s="26" t="n">
         <v>7.6</v>
@@ -15610,7 +15610,7 @@
       </c>
       <c r="Q300" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -15634,16 +15634,16 @@
         <v>2634</v>
       </c>
       <c r="I301" s="24" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J301" s="24" t="n">
-        <v>7727</v>
+        <v>7610</v>
       </c>
       <c r="K301" s="25" t="n">
-        <v>10.3</v>
+        <v>11.3</v>
       </c>
       <c r="L301" s="25" t="n">
-        <v>1288</v>
+        <v>1405</v>
       </c>
       <c r="M301" s="26" t="n">
         <v>6.6</v>
@@ -15683,16 +15683,16 @@
         <v>5565</v>
       </c>
       <c r="I302" s="24" t="n">
-        <v>64</v>
+        <v>63.2</v>
       </c>
       <c r="J302" s="24" t="n">
-        <v>14810</v>
+        <v>14631</v>
       </c>
       <c r="K302" s="25" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="L302" s="25" t="n">
-        <v>449</v>
+        <v>628</v>
       </c>
       <c r="M302" s="26" t="n">
         <v>10.1</v>
@@ -15781,16 +15781,16 @@
         <v>2488</v>
       </c>
       <c r="I304" s="24" t="n">
-        <v>69.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="J304" s="24" t="n">
-        <v>10074</v>
+        <v>10024</v>
       </c>
       <c r="K304" s="25" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="L304" s="25" t="n">
-        <v>109</v>
+        <v>160</v>
       </c>
       <c r="M304" s="26" t="n">
         <v>12.7</v>
@@ -15879,16 +15879,16 @@
         <v>679</v>
       </c>
       <c r="I306" s="24" t="n">
-        <v>72.90000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="J306" s="24" t="n">
-        <v>7317</v>
+        <v>7138</v>
       </c>
       <c r="K306" s="25" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="L306" s="25" t="n">
-        <v>412</v>
+        <v>591</v>
       </c>
       <c r="M306" s="26" t="n">
         <v>16.2</v>
@@ -15928,16 +15928,16 @@
         <v>3089</v>
       </c>
       <c r="I307" s="24" t="n">
-        <v>63.6</v>
+        <v>62.1</v>
       </c>
       <c r="J307" s="24" t="n">
-        <v>14332</v>
+        <v>13989</v>
       </c>
       <c r="K307" s="25" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="L307" s="25" t="n">
-        <v>840</v>
+        <v>1183</v>
       </c>
       <c r="M307" s="26" t="n">
         <v>19</v>
@@ -16124,16 +16124,16 @@
         <v>1414</v>
       </c>
       <c r="I311" s="24" t="n">
-        <v>69.7</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="J311" s="24" t="n">
-        <v>7726</v>
+        <v>7544</v>
       </c>
       <c r="K311" s="25" t="n">
-        <v>6.4</v>
+        <v>8.1</v>
       </c>
       <c r="L311" s="25" t="n">
-        <v>713</v>
+        <v>895</v>
       </c>
       <c r="M311" s="26" t="n">
         <v>11.1</v>
@@ -16271,16 +16271,16 @@
         <v>234235</v>
       </c>
       <c r="I314" s="24" t="n">
-        <v>16.5</v>
+        <v>14.3</v>
       </c>
       <c r="J314" s="24" t="n">
-        <v>58607</v>
+        <v>50805</v>
       </c>
       <c r="K314" s="25" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="L314" s="25" t="n">
-        <v>2031</v>
+        <v>9833</v>
       </c>
       <c r="M314" s="26" t="n">
         <v>16.9</v>
@@ -16320,16 +16320,16 @@
         <v>13893</v>
       </c>
       <c r="I315" s="24" t="n">
-        <v>41.7</v>
+        <v>38.1</v>
       </c>
       <c r="J315" s="24" t="n">
-        <v>15047</v>
+        <v>13750</v>
       </c>
       <c r="K315" s="25" t="n">
-        <v>2.3</v>
+        <v>5.9</v>
       </c>
       <c r="L315" s="25" t="n">
-        <v>825</v>
+        <v>2122</v>
       </c>
       <c r="M315" s="26" t="n">
         <v>17.5</v>
@@ -16345,7 +16345,7 @@
       </c>
       <c r="Q315" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -16369,16 +16369,16 @@
         <v>8095</v>
       </c>
       <c r="I316" s="24" t="n">
-        <v>49</v>
+        <v>41.7</v>
       </c>
       <c r="J316" s="24" t="n">
-        <v>12026</v>
+        <v>10251</v>
       </c>
       <c r="K316" s="25" t="n">
-        <v>1.7</v>
+        <v>8.9</v>
       </c>
       <c r="L316" s="25" t="n">
-        <v>418</v>
+        <v>2193</v>
       </c>
       <c r="M316" s="26" t="n">
         <v>16.4</v>
@@ -16394,7 +16394,7 @@
       </c>
       <c r="Q316" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -16418,16 +16418,16 @@
         <v>7608</v>
       </c>
       <c r="I317" s="24" t="n">
-        <v>65.90000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="J317" s="24" t="n">
-        <v>27166</v>
+        <v>25590</v>
       </c>
       <c r="K317" s="25" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="L317" s="25" t="n">
-        <v>591</v>
+        <v>2168</v>
       </c>
       <c r="M317" s="26" t="n">
         <v>14.2</v>
@@ -16467,16 +16467,16 @@
         <v>11095</v>
       </c>
       <c r="I318" s="24" t="n">
-        <v>52.4</v>
+        <v>46.8</v>
       </c>
       <c r="J318" s="24" t="n">
-        <v>25565</v>
+        <v>22847</v>
       </c>
       <c r="K318" s="25" t="n">
-        <v>0.9</v>
+        <v>6.4</v>
       </c>
       <c r="L318" s="25" t="n">
-        <v>418</v>
+        <v>3136</v>
       </c>
       <c r="M318" s="26" t="n">
         <v>24</v>
@@ -16516,16 +16516,16 @@
         <v>11178</v>
       </c>
       <c r="I319" s="24" t="n">
-        <v>56.7</v>
+        <v>48</v>
       </c>
       <c r="J319" s="24" t="n">
-        <v>26766</v>
+        <v>22652</v>
       </c>
       <c r="K319" s="25" t="n">
-        <v>3.3</v>
+        <v>12</v>
       </c>
       <c r="L319" s="25" t="n">
-        <v>1543</v>
+        <v>5657</v>
       </c>
       <c r="M319" s="26" t="n">
         <v>16.4</v>
@@ -16541,7 +16541,7 @@
       </c>
       <c r="Q319" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -16565,16 +16565,16 @@
         <v>3202</v>
       </c>
       <c r="I320" s="24" t="n">
-        <v>63.4</v>
+        <v>56.6</v>
       </c>
       <c r="J320" s="24" t="n">
-        <v>12474</v>
+        <v>11140</v>
       </c>
       <c r="K320" s="25" t="n">
-        <v>4.1</v>
+        <v>10.8</v>
       </c>
       <c r="L320" s="25" t="n">
-        <v>800</v>
+        <v>2135</v>
       </c>
       <c r="M320" s="26" t="n">
         <v>16.3</v>
@@ -16614,16 +16614,16 @@
         <v>4286</v>
       </c>
       <c r="I321" s="24" t="n">
-        <v>66</v>
+        <v>62.7</v>
       </c>
       <c r="J321" s="24" t="n">
-        <v>15507</v>
+        <v>14715</v>
       </c>
       <c r="K321" s="25" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="L321" s="25" t="n">
-        <v>238</v>
+        <v>1029</v>
       </c>
       <c r="M321" s="26" t="n">
         <v>14.7</v>
@@ -16712,16 +16712,16 @@
         <v>13543</v>
       </c>
       <c r="I323" s="24" t="n">
-        <v>56.6</v>
+        <v>48.7</v>
       </c>
       <c r="J323" s="24" t="n">
-        <v>26245</v>
+        <v>22569</v>
       </c>
       <c r="K323" s="25" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L323" s="25" t="n">
-        <v>479</v>
+        <v>4155</v>
       </c>
       <c r="M323" s="26" t="n">
         <v>13.1</v>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="Q323" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -16810,16 +16810,16 @@
         <v>2822</v>
       </c>
       <c r="I325" s="24" t="n">
-        <v>56.5</v>
+        <v>53.6</v>
       </c>
       <c r="J325" s="24" t="n">
-        <v>5861</v>
+        <v>5557</v>
       </c>
       <c r="K325" s="25" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="L325" s="25" t="n">
-        <v>43</v>
+        <v>347</v>
       </c>
       <c r="M325" s="26" t="n">
         <v>15.9</v>
@@ -16859,16 +16859,16 @@
         <v>500</v>
       </c>
       <c r="I326" s="24" t="n">
-        <v>82.8</v>
+        <v>77.3</v>
       </c>
       <c r="J326" s="24" t="n">
-        <v>9023</v>
+        <v>8423</v>
       </c>
       <c r="K326" s="25" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="L326" s="25" t="n">
-        <v>250</v>
+        <v>850</v>
       </c>
       <c r="M326" s="26" t="n">
         <v>10.4</v>
@@ -16908,16 +16908,16 @@
         <v>1487</v>
       </c>
       <c r="I327" s="24" t="n">
-        <v>46.4</v>
+        <v>44.2</v>
       </c>
       <c r="J327" s="24" t="n">
-        <v>2188</v>
+        <v>2086</v>
       </c>
       <c r="K327" s="25" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="L327" s="25" t="n">
-        <v>68</v>
+        <v>171</v>
       </c>
       <c r="M327" s="26" t="n">
         <v>20.7</v>
@@ -16957,16 +16957,16 @@
         <v>5755</v>
       </c>
       <c r="I328" s="24" t="n">
-        <v>53</v>
+        <v>51.9</v>
       </c>
       <c r="J328" s="24" t="n">
-        <v>15621</v>
+        <v>15313</v>
       </c>
       <c r="K328" s="25" t="n">
-        <v>6.6</v>
+        <v>7.7</v>
       </c>
       <c r="L328" s="25" t="n">
-        <v>1953</v>
+        <v>2261</v>
       </c>
       <c r="M328" s="26" t="n">
         <v>20.9</v>
@@ -17006,16 +17006,16 @@
         <v>484</v>
       </c>
       <c r="I329" s="24" t="n">
-        <v>53.5</v>
+        <v>52.8</v>
       </c>
       <c r="J329" s="24" t="n">
-        <v>1322</v>
+        <v>1305</v>
       </c>
       <c r="K329" s="25" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="L329" s="25" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="M329" s="26" t="n">
         <v>25.2</v>
@@ -17153,16 +17153,16 @@
         <v>7707</v>
       </c>
       <c r="I332" s="24" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="J332" s="24" t="n">
-        <v>2528</v>
+        <v>2491</v>
       </c>
       <c r="K332" s="25" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="L332" s="25" t="n">
-        <v>375</v>
+        <v>412</v>
       </c>
       <c r="M332" s="26" t="n">
         <v>18.3</v>
@@ -17300,16 +17300,16 @@
         <v>3275</v>
       </c>
       <c r="I335" s="24" t="n">
-        <v>16.3</v>
+        <v>16</v>
       </c>
       <c r="J335" s="24" t="n">
-        <v>807</v>
+        <v>790</v>
       </c>
       <c r="K335" s="25" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="L335" s="25" t="n">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="M335" s="26" t="n">
         <v>14.4</v>
@@ -17496,16 +17496,16 @@
         <v>8327</v>
       </c>
       <c r="I339" s="24" t="n">
-        <v>16.1</v>
+        <v>15.3</v>
       </c>
       <c r="J339" s="24" t="n">
-        <v>2021</v>
+        <v>1917</v>
       </c>
       <c r="K339" s="25" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="L339" s="25" t="n">
-        <v>259</v>
+        <v>363</v>
       </c>
       <c r="M339" s="26" t="n">
         <v>15.5</v>
@@ -17545,16 +17545,16 @@
         <v>14692</v>
       </c>
       <c r="I340" s="24" t="n">
-        <v>22.9</v>
+        <v>22.5</v>
       </c>
       <c r="J340" s="24" t="n">
-        <v>6090</v>
+        <v>5997</v>
       </c>
       <c r="K340" s="25" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="L340" s="25" t="n">
-        <v>480</v>
+        <v>573</v>
       </c>
       <c r="M340" s="26" t="n">
         <v>20.2</v>
@@ -18280,16 +18280,16 @@
         <v>112719</v>
       </c>
       <c r="I355" s="24" t="n">
-        <v>17.2</v>
+        <v>16.4</v>
       </c>
       <c r="J355" s="24" t="n">
-        <v>28696</v>
+        <v>27481</v>
       </c>
       <c r="K355" s="25" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="L355" s="25" t="n">
-        <v>2763</v>
+        <v>3978</v>
       </c>
       <c r="M355" s="26" t="n">
         <v>13.8</v>
@@ -18329,16 +18329,16 @@
         <v>59531</v>
       </c>
       <c r="I356" s="24" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="J356" s="24" t="n">
-        <v>62159</v>
+        <v>61614</v>
       </c>
       <c r="K356" s="25" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="L356" s="25" t="n">
-        <v>1639</v>
+        <v>2183</v>
       </c>
       <c r="M356" s="26" t="n">
         <v>17.2</v>
@@ -18525,16 +18525,16 @@
         <v>35205</v>
       </c>
       <c r="I360" s="24" t="n">
-        <v>38.2</v>
+        <v>37.9</v>
       </c>
       <c r="J360" s="24" t="n">
-        <v>35212</v>
+        <v>34921</v>
       </c>
       <c r="K360" s="25" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="L360" s="25" t="n">
-        <v>5234</v>
+        <v>5525</v>
       </c>
       <c r="M360" s="26" t="n">
         <v>18</v>
@@ -18819,16 +18819,16 @@
         <v>14412</v>
       </c>
       <c r="I366" s="24" t="n">
-        <v>61.1</v>
+        <v>60.9</v>
       </c>
       <c r="J366" s="24" t="n">
-        <v>43479</v>
+        <v>43279</v>
       </c>
       <c r="K366" s="25" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="L366" s="25" t="n">
-        <v>2202</v>
+        <v>2402</v>
       </c>
       <c r="M366" s="26" t="n">
         <v>15.5</v>
@@ -18917,16 +18917,16 @@
         <v>29221</v>
       </c>
       <c r="I368" s="24" t="n">
-        <v>24.5</v>
+        <v>23.9</v>
       </c>
       <c r="J368" s="24" t="n">
-        <v>10452</v>
+        <v>10207</v>
       </c>
       <c r="K368" s="25" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L368" s="25" t="n">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="M368" s="26" t="n">
         <v>7.1</v>
@@ -19015,16 +19015,16 @@
         <v>1091</v>
       </c>
       <c r="I370" s="24" t="n">
-        <v>76.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="J370" s="24" t="n">
-        <v>11636</v>
+        <v>11591</v>
       </c>
       <c r="K370" s="25" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="L370" s="25" t="n">
-        <v>364</v>
+        <v>409</v>
       </c>
       <c r="M370" s="26" t="n">
         <v>13.5</v>
@@ -19309,16 +19309,16 @@
         <v>73080</v>
       </c>
       <c r="I376" s="24" t="n">
-        <v>16.4</v>
+        <v>15.9</v>
       </c>
       <c r="J376" s="24" t="n">
-        <v>19652</v>
+        <v>19076</v>
       </c>
       <c r="K376" s="25" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="L376" s="25" t="n">
-        <v>3979</v>
+        <v>4554</v>
       </c>
       <c r="M376" s="26" t="n">
         <v>19.4</v>
@@ -19358,16 +19358,16 @@
         <v>63100</v>
       </c>
       <c r="I377" s="24" t="n">
-        <v>25</v>
+        <v>24.6</v>
       </c>
       <c r="J377" s="24" t="n">
-        <v>25849</v>
+        <v>25450</v>
       </c>
       <c r="K377" s="25" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="L377" s="25" t="n">
-        <v>2396</v>
+        <v>2796</v>
       </c>
       <c r="M377" s="26" t="n">
         <v>11.7</v>
@@ -19946,16 +19946,16 @@
         <v>6673</v>
       </c>
       <c r="I389" s="24" t="n">
-        <v>52.4</v>
+        <v>49.2</v>
       </c>
       <c r="J389" s="24" t="n">
-        <v>10322</v>
+        <v>9697</v>
       </c>
       <c r="K389" s="25" t="n">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="L389" s="25" t="n">
-        <v>417</v>
+        <v>1042</v>
       </c>
       <c r="M389" s="26" t="n">
         <v>11.6</v>
@@ -20047,13 +20047,13 @@
         <v>12.2</v>
       </c>
       <c r="J391" s="24" t="n">
-        <v>10970</v>
+        <v>10966</v>
       </c>
       <c r="K391" s="25" t="n">
         <v>6.1</v>
       </c>
       <c r="L391" s="25" t="n">
-        <v>5493</v>
+        <v>5497</v>
       </c>
       <c r="M391" s="26" t="n">
         <v>14.8</v>
@@ -20142,16 +20142,16 @@
         <v>459</v>
       </c>
       <c r="I393" s="24" t="n">
-        <v>64.09999999999999</v>
+        <v>63.7</v>
       </c>
       <c r="J393" s="24" t="n">
-        <v>11356</v>
+        <v>11280</v>
       </c>
       <c r="K393" s="25" t="n">
-        <v>18.4</v>
+        <v>18.8</v>
       </c>
       <c r="L393" s="25" t="n">
-        <v>3252</v>
+        <v>3328</v>
       </c>
       <c r="M393" s="26" t="n">
         <v>14.9</v>
@@ -20191,16 +20191,16 @@
         <v>6042</v>
       </c>
       <c r="I394" s="24" t="n">
-        <v>32.3</v>
+        <v>30.8</v>
       </c>
       <c r="J394" s="24" t="n">
-        <v>4296</v>
+        <v>4107</v>
       </c>
       <c r="K394" s="25" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="L394" s="25" t="n">
-        <v>1008</v>
+        <v>1196</v>
       </c>
       <c r="M394" s="26" t="n">
         <v>14.8</v>
@@ -20289,16 +20289,16 @@
         <v>7475</v>
       </c>
       <c r="I396" s="24" t="n">
-        <v>60.4</v>
+        <v>59.2</v>
       </c>
       <c r="J396" s="24" t="n">
-        <v>23553</v>
+        <v>23076</v>
       </c>
       <c r="K396" s="25" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="L396" s="25" t="n">
-        <v>2636</v>
+        <v>3113</v>
       </c>
       <c r="M396" s="26" t="n">
         <v>13.6</v>
@@ -20338,16 +20338,16 @@
         <v>8216</v>
       </c>
       <c r="I397" s="24" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J397" s="24" t="n">
-        <v>847</v>
+        <v>805</v>
       </c>
       <c r="K397" s="25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="L397" s="25" t="n">
-        <v>974</v>
+        <v>1016</v>
       </c>
       <c r="M397" s="26" t="n">
         <v>15.1</v>
@@ -20485,16 +20485,16 @@
         <v>0</v>
       </c>
       <c r="I400" s="24" t="n">
-        <v>75.5</v>
+        <v>65</v>
       </c>
       <c r="J400" s="24" t="n">
-        <v>21968</v>
+        <v>18901</v>
       </c>
       <c r="K400" s="25" t="n">
-        <v>6.1</v>
+        <v>16.7</v>
       </c>
       <c r="L400" s="25" t="n">
-        <v>1781</v>
+        <v>4849</v>
       </c>
       <c r="M400" s="26" t="n">
         <v>18.4</v>
@@ -20534,16 +20534,16 @@
         <v>14824</v>
       </c>
       <c r="I401" s="24" t="n">
-        <v>38.3</v>
+        <v>37.9</v>
       </c>
       <c r="J401" s="24" t="n">
-        <v>15089</v>
+        <v>14957</v>
       </c>
       <c r="K401" s="25" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="L401" s="25" t="n">
-        <v>1324</v>
+        <v>1456</v>
       </c>
       <c r="M401" s="26" t="n">
         <v>20.8</v>
@@ -21114,16 +21114,16 @@
         <v>158111</v>
       </c>
       <c r="J9" s="24" t="n">
-        <v>13.4</v>
+        <v>12.9</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>28148</v>
+        <v>27090</v>
       </c>
       <c r="L9" s="25" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="M9" s="25" t="n">
-        <v>3245</v>
+        <v>4302</v>
       </c>
       <c r="N9" s="26" t="n">
         <v>9.699999999999999</v>
@@ -21222,13 +21222,13 @@
         <v>0</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>28.6</v>
+        <v>23.8</v>
       </c>
       <c r="K11" s="24" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="25" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M11" s="25" t="n">
         <v>0</v>
@@ -21708,16 +21708,16 @@
         <v>41775</v>
       </c>
       <c r="J20" s="24" t="n">
-        <v>33.8</v>
+        <v>32.9</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>32452</v>
+        <v>31595</v>
       </c>
       <c r="L20" s="25" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="M20" s="25" t="n">
-        <v>4551</v>
+        <v>5408</v>
       </c>
       <c r="N20" s="26" t="n">
         <v>18</v>
@@ -21762,16 +21762,16 @@
         <v>17408</v>
       </c>
       <c r="J21" s="24" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="K21" s="24" t="n">
-        <v>6037</v>
+        <v>6002</v>
       </c>
       <c r="L21" s="25" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M21" s="25" t="n">
-        <v>1795</v>
+        <v>1830</v>
       </c>
       <c r="N21" s="26" t="n">
         <v>7.7</v>
@@ -22518,16 +22518,16 @@
         <v>26652</v>
       </c>
       <c r="J35" s="24" t="n">
-        <v>63.1</v>
+        <v>61.7</v>
       </c>
       <c r="K35" s="24" t="n">
-        <v>53001</v>
+        <v>51896</v>
       </c>
       <c r="L35" s="25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M35" s="25" t="n">
-        <v>24</v>
+        <v>1129</v>
       </c>
       <c r="N35" s="26" t="n">
         <v>5.2</v>
@@ -23490,16 +23490,16 @@
         <v>62243</v>
       </c>
       <c r="J53" s="24" t="n">
-        <v>13.4</v>
+        <v>12</v>
       </c>
       <c r="K53" s="24" t="n">
-        <v>13304</v>
+        <v>11910</v>
       </c>
       <c r="L53" s="25" t="n">
-        <v>4.9</v>
+        <v>6.3</v>
       </c>
       <c r="M53" s="25" t="n">
-        <v>4879</v>
+        <v>6273</v>
       </c>
       <c r="N53" s="26" t="n">
         <v>19.2</v>
@@ -24033,13 +24033,13 @@
         <v>14.3</v>
       </c>
       <c r="K63" s="24" t="n">
-        <v>44620</v>
+        <v>44535</v>
       </c>
       <c r="L63" s="25" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="M63" s="25" t="n">
-        <v>1334</v>
+        <v>1419</v>
       </c>
       <c r="N63" s="26" t="n">
         <v>18.4</v>
@@ -24408,16 +24408,16 @@
         <v>78681</v>
       </c>
       <c r="J70" s="24" t="n">
-        <v>17.8</v>
+        <v>17.1</v>
       </c>
       <c r="K70" s="24" t="n">
-        <v>20570</v>
+        <v>19676</v>
       </c>
       <c r="L70" s="25" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="M70" s="25" t="n">
-        <v>1788</v>
+        <v>2681</v>
       </c>
       <c r="N70" s="26" t="n">
         <v>12.4</v>
@@ -24681,13 +24681,13 @@
         <v>15.6</v>
       </c>
       <c r="K75" s="24" t="n">
-        <v>8402</v>
+        <v>8392</v>
       </c>
       <c r="L75" s="25" t="n">
         <v>0.1</v>
       </c>
       <c r="M75" s="25" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="N75" s="26" t="n">
         <v>20.3</v>
@@ -24897,13 +24897,13 @@
         <v>6</v>
       </c>
       <c r="K79" s="24" t="n">
-        <v>2509</v>
+        <v>2505</v>
       </c>
       <c r="L79" s="25" t="n">
         <v>1.5</v>
       </c>
       <c r="M79" s="25" t="n">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="N79" s="26" t="n">
         <v>14.7</v>
@@ -25391,16 +25391,16 @@
         <v>14096</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>18.1</v>
+        <v>17.6</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>4060</v>
+        <v>3947</v>
       </c>
       <c r="L11" s="25" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M11" s="25" t="n">
-        <v>338</v>
+        <v>451</v>
       </c>
       <c r="N11" s="26" t="n">
         <v>17.6</v>
@@ -25445,16 +25445,16 @@
         <v>5356</v>
       </c>
       <c r="J12" s="24" t="n">
-        <v>16.9</v>
+        <v>16.5</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>1393</v>
+        <v>1362</v>
       </c>
       <c r="L12" s="25" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="M12" s="25" t="n">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="N12" s="26" t="n">
         <v>17.3</v>
@@ -25553,16 +25553,16 @@
         <v>4166</v>
       </c>
       <c r="J14" s="24" t="n">
-        <v>34.5</v>
+        <v>34.1</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>2850</v>
+        <v>2819</v>
       </c>
       <c r="L14" s="25" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="M14" s="25" t="n">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="N14" s="26" t="n">
         <v>13.3</v>
@@ -25877,16 +25877,16 @@
         <v>19468</v>
       </c>
       <c r="J20" s="24" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>3729</v>
+        <v>3580</v>
       </c>
       <c r="L20" s="25" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M20" s="25" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="N20" s="26" t="n">
         <v>22.3</v>
@@ -26093,16 +26093,16 @@
         <v>32253</v>
       </c>
       <c r="J24" s="24" t="n">
-        <v>23.5</v>
+        <v>22.2</v>
       </c>
       <c r="K24" s="24" t="n">
-        <v>11515</v>
+        <v>10891</v>
       </c>
       <c r="L24" s="25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M24" s="25" t="n">
-        <v>0</v>
+        <v>625</v>
       </c>
       <c r="N24" s="26" t="n">
         <v>10.7</v>
@@ -26147,16 +26147,16 @@
         <v>10464</v>
       </c>
       <c r="J25" s="24" t="n">
-        <v>25.3</v>
+        <v>24.9</v>
       </c>
       <c r="K25" s="24" t="n">
-        <v>4812</v>
+        <v>4733</v>
       </c>
       <c r="L25" s="25" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="M25" s="25" t="n">
-        <v>321</v>
+        <v>399</v>
       </c>
       <c r="N25" s="26" t="n">
         <v>18</v>
@@ -26172,7 +26172,7 @@
       </c>
       <c r="R25" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -26309,16 +26309,16 @@
         <v>12119</v>
       </c>
       <c r="J28" s="24" t="n">
-        <v>33</v>
+        <v>31.1</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>8101</v>
+        <v>7650</v>
       </c>
       <c r="L28" s="25" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="M28" s="25" t="n">
-        <v>225</v>
+        <v>675</v>
       </c>
       <c r="N28" s="26" t="n">
         <v>16.8</v>
@@ -26687,16 +26687,16 @@
         <v>7798</v>
       </c>
       <c r="J35" s="24" t="n">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
       <c r="K35" s="24" t="n">
-        <v>1535</v>
+        <v>1493</v>
       </c>
       <c r="L35" s="25" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="M35" s="25" t="n">
-        <v>581</v>
+        <v>622</v>
       </c>
       <c r="N35" s="26" t="n">
         <v>14.6</v>
@@ -27227,16 +27227,16 @@
         <v>34000</v>
       </c>
       <c r="J45" s="24" t="n">
-        <v>26.1</v>
+        <v>25.5</v>
       </c>
       <c r="K45" s="24" t="n">
-        <v>13742</v>
+        <v>13464</v>
       </c>
       <c r="L45" s="25" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M45" s="25" t="n">
-        <v>9</v>
+        <v>287</v>
       </c>
       <c r="N45" s="26" t="n">
         <v>9.4</v>
@@ -27335,16 +27335,16 @@
         <v>16720</v>
       </c>
       <c r="J47" s="24" t="n">
-        <v>15.9</v>
+        <v>15</v>
       </c>
       <c r="K47" s="24" t="n">
-        <v>3612</v>
+        <v>3406</v>
       </c>
       <c r="L47" s="25" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="M47" s="25" t="n">
-        <v>206</v>
+        <v>413</v>
       </c>
       <c r="N47" s="26" t="n">
         <v>9.5</v>
@@ -27443,16 +27443,16 @@
         <v>34028</v>
       </c>
       <c r="J49" s="24" t="n">
-        <v>20.2</v>
+        <v>18.5</v>
       </c>
       <c r="K49" s="24" t="n">
-        <v>9650</v>
+        <v>8869</v>
       </c>
       <c r="L49" s="25" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="M49" s="25" t="n">
-        <v>206</v>
+        <v>988</v>
       </c>
       <c r="N49" s="26" t="n">
         <v>8.300000000000001</v>
@@ -27551,16 +27551,16 @@
         <v>12528</v>
       </c>
       <c r="J51" s="24" t="n">
-        <v>16.9</v>
+        <v>15.5</v>
       </c>
       <c r="K51" s="24" t="n">
-        <v>2848</v>
+        <v>2614</v>
       </c>
       <c r="L51" s="25" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="M51" s="25" t="n">
-        <v>85</v>
+        <v>318</v>
       </c>
       <c r="N51" s="26" t="n">
         <v>8.4</v>
@@ -27605,16 +27605,16 @@
         <v>14749</v>
       </c>
       <c r="J52" s="24" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="K52" s="24" t="n">
-        <v>4667</v>
+        <v>4661</v>
       </c>
       <c r="L52" s="25" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="M52" s="25" t="n">
-        <v>1133</v>
+        <v>1139</v>
       </c>
       <c r="N52" s="26" t="n">
         <v>16</v>
@@ -27662,13 +27662,13 @@
         <v>41.2</v>
       </c>
       <c r="K53" s="24" t="n">
-        <v>25723</v>
+        <v>25713</v>
       </c>
       <c r="L53" s="25" t="n">
         <v>1.8</v>
       </c>
       <c r="M53" s="25" t="n">
-        <v>1136</v>
+        <v>1146</v>
       </c>
       <c r="N53" s="26" t="n">
         <v>14</v>
@@ -27767,16 +27767,16 @@
         <v>38149</v>
       </c>
       <c r="J55" s="24" t="n">
-        <v>22.3</v>
+        <v>21.4</v>
       </c>
       <c r="K55" s="24" t="n">
-        <v>14810</v>
+        <v>14216</v>
       </c>
       <c r="L55" s="25" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="M55" s="25" t="n">
-        <v>3218</v>
+        <v>3812</v>
       </c>
       <c r="N55" s="26" t="n">
         <v>15.6</v>
@@ -27875,16 +27875,16 @@
         <v>40544</v>
       </c>
       <c r="J57" s="24" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="K57" s="24" t="n">
-        <v>17348</v>
+        <v>17172</v>
       </c>
       <c r="L57" s="25" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="M57" s="25" t="n">
-        <v>1237</v>
+        <v>1414</v>
       </c>
       <c r="N57" s="26" t="n">
         <v>14.3</v>
@@ -27929,16 +27929,16 @@
         <v>74918</v>
       </c>
       <c r="J58" s="24" t="n">
-        <v>27.7</v>
+        <v>27.4</v>
       </c>
       <c r="K58" s="24" t="n">
-        <v>35926</v>
+        <v>35488</v>
       </c>
       <c r="L58" s="25" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="M58" s="25" t="n">
-        <v>2629</v>
+        <v>3067</v>
       </c>
       <c r="N58" s="26" t="n">
         <v>12.5</v>
@@ -27983,16 +27983,16 @@
         <v>31688</v>
       </c>
       <c r="J59" s="24" t="n">
-        <v>43.1</v>
+        <v>42.6</v>
       </c>
       <c r="K59" s="24" t="n">
-        <v>34921</v>
+        <v>34534</v>
       </c>
       <c r="L59" s="25" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="M59" s="25" t="n">
-        <v>2569</v>
+        <v>2955</v>
       </c>
       <c r="N59" s="26" t="n">
         <v>14.6</v>
@@ -28037,16 +28037,16 @@
         <v>15996</v>
       </c>
       <c r="J60" s="24" t="n">
-        <v>31</v>
+        <v>30.1</v>
       </c>
       <c r="K60" s="24" t="n">
-        <v>10488</v>
+        <v>10187</v>
       </c>
       <c r="L60" s="25" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="M60" s="25" t="n">
-        <v>834</v>
+        <v>1135</v>
       </c>
       <c r="N60" s="26" t="n">
         <v>19.2</v>
@@ -28145,16 +28145,16 @@
         <v>13601</v>
       </c>
       <c r="J62" s="24" t="n">
-        <v>37.1</v>
+        <v>35.6</v>
       </c>
       <c r="K62" s="24" t="n">
-        <v>12903</v>
+        <v>12374</v>
       </c>
       <c r="L62" s="25" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="M62" s="25" t="n">
-        <v>1621</v>
+        <v>2150</v>
       </c>
       <c r="N62" s="26" t="n">
         <v>19.1</v>
@@ -28199,16 +28199,16 @@
         <v>26556</v>
       </c>
       <c r="J63" s="24" t="n">
-        <v>23.7</v>
+        <v>23.1</v>
       </c>
       <c r="K63" s="24" t="n">
-        <v>10584</v>
+        <v>10304</v>
       </c>
       <c r="L63" s="25" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="M63" s="25" t="n">
-        <v>735</v>
+        <v>1015</v>
       </c>
       <c r="N63" s="26" t="n">
         <v>15.2</v>
@@ -28253,16 +28253,16 @@
         <v>12226</v>
       </c>
       <c r="J64" s="24" t="n">
-        <v>46.9</v>
+        <v>46.7</v>
       </c>
       <c r="K64" s="24" t="n">
-        <v>18120</v>
+        <v>18012</v>
       </c>
       <c r="L64" s="25" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="M64" s="25" t="n">
-        <v>2811</v>
+        <v>2919</v>
       </c>
       <c r="N64" s="26" t="n">
         <v>14.1</v>
@@ -28307,16 +28307,16 @@
         <v>19448</v>
       </c>
       <c r="J65" s="24" t="n">
-        <v>62.5</v>
+        <v>61</v>
       </c>
       <c r="K65" s="24" t="n">
-        <v>56695</v>
+        <v>55326</v>
       </c>
       <c r="L65" s="25" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="M65" s="25" t="n">
-        <v>2190</v>
+        <v>3559</v>
       </c>
       <c r="N65" s="26" t="n">
         <v>13.6</v>
@@ -28361,16 +28361,16 @@
         <v>40962</v>
       </c>
       <c r="J66" s="24" t="n">
-        <v>23.1</v>
+        <v>22</v>
       </c>
       <c r="K66" s="24" t="n">
-        <v>16520</v>
+        <v>15730</v>
       </c>
       <c r="L66" s="25" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="M66" s="25" t="n">
-        <v>2953</v>
+        <v>3743</v>
       </c>
       <c r="N66" s="26" t="n">
         <v>15.4</v>
@@ -28386,7 +28386,7 @@
       </c>
       <c r="R66" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -28415,16 +28415,16 @@
         <v>28314</v>
       </c>
       <c r="J67" s="24" t="n">
-        <v>27.7</v>
+        <v>27.5</v>
       </c>
       <c r="K67" s="24" t="n">
-        <v>14821</v>
+        <v>14684</v>
       </c>
       <c r="L67" s="25" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="M67" s="25" t="n">
-        <v>1543</v>
+        <v>1679</v>
       </c>
       <c r="N67" s="26" t="n">
         <v>16.5</v>
@@ -28469,16 +28469,16 @@
         <v>9309</v>
       </c>
       <c r="J68" s="24" t="n">
-        <v>44.1</v>
+        <v>42.6</v>
       </c>
       <c r="K68" s="24" t="n">
-        <v>11402</v>
+        <v>11025</v>
       </c>
       <c r="L68" s="25" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="M68" s="25" t="n">
-        <v>829</v>
+        <v>1206</v>
       </c>
       <c r="N68" s="26" t="n">
         <v>16.7</v>
@@ -28494,7 +28494,7 @@
       </c>
       <c r="R68" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -28577,16 +28577,16 @@
         <v>11174</v>
       </c>
       <c r="J70" s="24" t="n">
-        <v>28.7</v>
+        <v>27.9</v>
       </c>
       <c r="K70" s="24" t="n">
-        <v>6282</v>
+        <v>6094</v>
       </c>
       <c r="L70" s="25" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="M70" s="25" t="n">
-        <v>438</v>
+        <v>625</v>
       </c>
       <c r="N70" s="26" t="n">
         <v>18.1</v>
@@ -28631,16 +28631,16 @@
         <v>8318</v>
       </c>
       <c r="J71" s="24" t="n">
-        <v>56.2</v>
+        <v>51.2</v>
       </c>
       <c r="K71" s="24" t="n">
-        <v>20539</v>
+        <v>18727</v>
       </c>
       <c r="L71" s="25" t="n">
-        <v>4.1</v>
+        <v>9</v>
       </c>
       <c r="M71" s="25" t="n">
-        <v>1493</v>
+        <v>3306</v>
       </c>
       <c r="N71" s="26" t="n">
         <v>17</v>
@@ -28685,16 +28685,16 @@
         <v>8942</v>
       </c>
       <c r="J72" s="24" t="n">
-        <v>34.8</v>
+        <v>34.5</v>
       </c>
       <c r="K72" s="24" t="n">
-        <v>7552</v>
+        <v>7481</v>
       </c>
       <c r="L72" s="25" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="M72" s="25" t="n">
-        <v>1490</v>
+        <v>1561</v>
       </c>
       <c r="N72" s="26" t="n">
         <v>17.1</v>
@@ -28793,16 +28793,16 @@
         <v>63057</v>
       </c>
       <c r="J74" s="24" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="K74" s="24" t="n">
-        <v>8128</v>
+        <v>7603</v>
       </c>
       <c r="L74" s="25" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="M74" s="25" t="n">
-        <v>185</v>
+        <v>710</v>
       </c>
       <c r="N74" s="26" t="n">
         <v>19.7</v>
@@ -28818,7 +28818,7 @@
       </c>
       <c r="R74" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -28847,16 +28847,16 @@
         <v>39796</v>
       </c>
       <c r="J75" s="24" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="K75" s="24" t="n">
-        <v>8013</v>
+        <v>7886</v>
       </c>
       <c r="L75" s="25" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M75" s="25" t="n">
-        <v>9</v>
+        <v>136</v>
       </c>
       <c r="N75" s="26" t="n">
         <v>14.7</v>
@@ -28955,16 +28955,16 @@
         <v>25434</v>
       </c>
       <c r="J77" s="24" t="n">
-        <v>22.5</v>
+        <v>20.8</v>
       </c>
       <c r="K77" s="24" t="n">
-        <v>8611</v>
+        <v>7964</v>
       </c>
       <c r="L77" s="25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M77" s="25" t="n">
-        <v>0</v>
+        <v>647</v>
       </c>
       <c r="N77" s="26" t="n">
         <v>11.1</v>
@@ -29333,16 +29333,16 @@
         <v>8592</v>
       </c>
       <c r="J84" s="24" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="K84" s="24" t="n">
-        <v>263</v>
+        <v>234</v>
       </c>
       <c r="L84" s="25" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="M84" s="25" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="N84" s="26" t="n">
         <v>5.3</v>
@@ -30791,16 +30791,16 @@
         <v>13024</v>
       </c>
       <c r="J111" s="24" t="n">
-        <v>37.6</v>
+        <v>35.7</v>
       </c>
       <c r="K111" s="24" t="n">
-        <v>10545</v>
+        <v>10018</v>
       </c>
       <c r="L111" s="25" t="n">
-        <v>5.2</v>
+        <v>7.1</v>
       </c>
       <c r="M111" s="25" t="n">
-        <v>1457</v>
+        <v>1984</v>
       </c>
       <c r="N111" s="26" t="n">
         <v>10.8</v>
@@ -30953,16 +30953,16 @@
         <v>4471</v>
       </c>
       <c r="J114" s="24" t="n">
-        <v>36.1</v>
+        <v>35</v>
       </c>
       <c r="K114" s="24" t="n">
-        <v>3430</v>
+        <v>3322</v>
       </c>
       <c r="L114" s="25" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="M114" s="25" t="n">
-        <v>539</v>
+        <v>646</v>
       </c>
       <c r="N114" s="26" t="n">
         <v>11.1</v>
@@ -31169,16 +31169,16 @@
         <v>9248</v>
       </c>
       <c r="J118" s="24" t="n">
-        <v>30.1</v>
+        <v>29.8</v>
       </c>
       <c r="K118" s="24" t="n">
-        <v>5287</v>
+        <v>5228</v>
       </c>
       <c r="L118" s="25" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="M118" s="25" t="n">
-        <v>471</v>
+        <v>530</v>
       </c>
       <c r="N118" s="26" t="n">
         <v>14.5</v>
@@ -31763,16 +31763,16 @@
         <v>5310</v>
       </c>
       <c r="J129" s="24" t="n">
-        <v>36.1</v>
+        <v>34.7</v>
       </c>
       <c r="K129" s="24" t="n">
-        <v>3892</v>
+        <v>3744</v>
       </c>
       <c r="L129" s="25" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="M129" s="25" t="n">
-        <v>119</v>
+        <v>267</v>
       </c>
       <c r="N129" s="26" t="n">
         <v>13.6</v>
@@ -31817,16 +31817,16 @@
         <v>2613</v>
       </c>
       <c r="J130" s="24" t="n">
-        <v>44.3</v>
+        <v>43.8</v>
       </c>
       <c r="K130" s="24" t="n">
-        <v>2744</v>
+        <v>2711</v>
       </c>
       <c r="L130" s="25" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="M130" s="25" t="n">
-        <v>115</v>
+        <v>148</v>
       </c>
       <c r="N130" s="26" t="n">
         <v>11.7</v>
@@ -32087,16 +32087,16 @@
         <v>3843</v>
       </c>
       <c r="J135" s="24" t="n">
-        <v>46</v>
+        <v>45.7</v>
       </c>
       <c r="K135" s="24" t="n">
-        <v>4764</v>
+        <v>4732</v>
       </c>
       <c r="L135" s="25" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="M135" s="25" t="n">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="N135" s="26" t="n">
         <v>15</v>
@@ -32249,16 +32249,16 @@
         <v>3957</v>
       </c>
       <c r="J138" s="24" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
       <c r="K138" s="24" t="n">
-        <v>674</v>
+        <v>659</v>
       </c>
       <c r="L138" s="25" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="M138" s="25" t="n">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="N138" s="26" t="n">
         <v>8.699999999999999</v>
@@ -32303,16 +32303,16 @@
         <v>463</v>
       </c>
       <c r="J139" s="24" t="n">
-        <v>72.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="K139" s="24" t="n">
-        <v>11397</v>
+        <v>11339</v>
       </c>
       <c r="L139" s="25" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="M139" s="25" t="n">
-        <v>1621</v>
+        <v>1679</v>
       </c>
       <c r="N139" s="26" t="n">
         <v>14.1</v>
@@ -32357,16 +32357,16 @@
         <v>2253</v>
       </c>
       <c r="J140" s="24" t="n">
-        <v>57.2</v>
+        <v>55.8</v>
       </c>
       <c r="K140" s="24" t="n">
-        <v>4186</v>
+        <v>4079</v>
       </c>
       <c r="L140" s="25" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="M140" s="25" t="n">
-        <v>43</v>
+        <v>150</v>
       </c>
       <c r="N140" s="26" t="n">
         <v>11.4</v>
@@ -32465,16 +32465,16 @@
         <v>2905</v>
       </c>
       <c r="J142" s="24" t="n">
-        <v>57.3</v>
+        <v>56.9</v>
       </c>
       <c r="K142" s="24" t="n">
-        <v>7662</v>
+        <v>7612</v>
       </c>
       <c r="L142" s="25" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="M142" s="25" t="n">
-        <v>801</v>
+        <v>851</v>
       </c>
       <c r="N142" s="26" t="n">
         <v>15</v>
@@ -32627,16 +32627,16 @@
         <v>27453</v>
       </c>
       <c r="J145" s="24" t="n">
-        <v>25.1</v>
+        <v>24.6</v>
       </c>
       <c r="K145" s="24" t="n">
-        <v>12296</v>
+        <v>12035</v>
       </c>
       <c r="L145" s="25" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="M145" s="25" t="n">
-        <v>1567</v>
+        <v>1828</v>
       </c>
       <c r="N145" s="26" t="n">
         <v>15.5</v>
@@ -32735,16 +32735,16 @@
         <v>28465</v>
       </c>
       <c r="J147" s="24" t="n">
-        <v>37</v>
+        <v>32.7</v>
       </c>
       <c r="K147" s="24" t="n">
-        <v>22316</v>
+        <v>19732</v>
       </c>
       <c r="L147" s="25" t="n">
-        <v>3.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M147" s="25" t="n">
-        <v>2375</v>
+        <v>4960</v>
       </c>
       <c r="N147" s="26" t="n">
         <v>11.9</v>
@@ -32760,7 +32760,7 @@
       </c>
       <c r="R147" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -32789,16 +32789,16 @@
         <v>2150</v>
       </c>
       <c r="J148" s="24" t="n">
-        <v>53.2</v>
+        <v>52.9</v>
       </c>
       <c r="K148" s="24" t="n">
-        <v>3863</v>
+        <v>3842</v>
       </c>
       <c r="L148" s="25" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="M148" s="25" t="n">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="N148" s="26" t="n">
         <v>13.8</v>
@@ -33059,16 +33059,16 @@
         <v>3077</v>
       </c>
       <c r="J153" s="24" t="n">
-        <v>74.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K153" s="24" t="n">
-        <v>19909</v>
+        <v>18310</v>
       </c>
       <c r="L153" s="25" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M153" s="25" t="n">
-        <v>799</v>
+        <v>2398</v>
       </c>
       <c r="N153" s="26" t="n">
         <v>10.9</v>
@@ -33221,16 +33221,16 @@
         <v>19975</v>
       </c>
       <c r="J156" s="24" t="n">
-        <v>46.2</v>
+        <v>42.8</v>
       </c>
       <c r="K156" s="24" t="n">
-        <v>19905</v>
+        <v>18461</v>
       </c>
       <c r="L156" s="25" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="M156" s="25" t="n">
-        <v>178</v>
+        <v>1623</v>
       </c>
       <c r="N156" s="26" t="n">
         <v>7</v>
@@ -33275,16 +33275,16 @@
         <v>34047</v>
       </c>
       <c r="J157" s="24" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K157" s="24" t="n">
-        <v>11423</v>
+        <v>8442</v>
       </c>
       <c r="L157" s="25" t="n">
-        <v>0.8</v>
+        <v>6.8</v>
       </c>
       <c r="M157" s="25" t="n">
-        <v>402</v>
+        <v>3383</v>
       </c>
       <c r="N157" s="26" t="n">
         <v>7.6</v>
@@ -33329,16 +33329,16 @@
         <v>17047</v>
       </c>
       <c r="J158" s="24" t="n">
-        <v>30</v>
+        <v>19.4</v>
       </c>
       <c r="K158" s="24" t="n">
-        <v>9533</v>
+        <v>6184</v>
       </c>
       <c r="L158" s="25" t="n">
-        <v>0.4</v>
+        <v>11</v>
       </c>
       <c r="M158" s="25" t="n">
-        <v>139</v>
+        <v>3489</v>
       </c>
       <c r="N158" s="26" t="n">
         <v>16</v>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="R158" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -33383,16 +33383,16 @@
         <v>6471</v>
       </c>
       <c r="J159" s="24" t="n">
-        <v>82.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K159" s="24" t="n">
-        <v>33670</v>
+        <v>33551</v>
       </c>
       <c r="L159" s="25" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="M159" s="25" t="n">
-        <v>238</v>
+        <v>357</v>
       </c>
       <c r="N159" s="26" t="n">
         <v>0.9</v>
@@ -33437,16 +33437,16 @@
         <v>4753</v>
       </c>
       <c r="J160" s="24" t="n">
-        <v>66</v>
+        <v>65.8</v>
       </c>
       <c r="K160" s="24" t="n">
-        <v>20191</v>
+        <v>20108</v>
       </c>
       <c r="L160" s="25" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="M160" s="25" t="n">
-        <v>331</v>
+        <v>413</v>
       </c>
       <c r="N160" s="26" t="n">
         <v>17.4</v>
@@ -33491,16 +33491,16 @@
         <v>17991</v>
       </c>
       <c r="J161" s="24" t="n">
-        <v>27.1</v>
+        <v>26.1</v>
       </c>
       <c r="K161" s="24" t="n">
-        <v>8357</v>
+        <v>8044</v>
       </c>
       <c r="L161" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M161" s="25" t="n">
-        <v>313</v>
+        <v>627</v>
       </c>
       <c r="N161" s="26" t="n">
         <v>13.6</v>
@@ -33653,16 +33653,16 @@
         <v>18658</v>
       </c>
       <c r="J164" s="24" t="n">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K164" s="24" t="n">
-        <v>1938</v>
+        <v>1858</v>
       </c>
       <c r="L164" s="25" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M164" s="25" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="N164" s="26" t="n">
         <v>7.9</v>
@@ -33707,16 +33707,16 @@
         <v>67</v>
       </c>
       <c r="J165" s="24" t="n">
-        <v>85.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="K165" s="24" t="n">
-        <v>5881</v>
+        <v>5547</v>
       </c>
       <c r="L165" s="25" t="n">
-        <v>2</v>
+        <v>6.8</v>
       </c>
       <c r="M165" s="25" t="n">
-        <v>134</v>
+        <v>468</v>
       </c>
       <c r="N165" s="26" t="n">
         <v>11.2</v>
@@ -33761,16 +33761,16 @@
         <v>19761</v>
       </c>
       <c r="J166" s="24" t="n">
-        <v>35.1</v>
+        <v>29.8</v>
       </c>
       <c r="K166" s="24" t="n">
-        <v>13039</v>
+        <v>11083</v>
       </c>
       <c r="L166" s="25" t="n">
-        <v>0.8</v>
+        <v>6.1</v>
       </c>
       <c r="M166" s="25" t="n">
-        <v>301</v>
+        <v>2257</v>
       </c>
       <c r="N166" s="26" t="n">
         <v>11</v>
@@ -33815,16 +33815,16 @@
         <v>2896</v>
       </c>
       <c r="J167" s="24" t="n">
-        <v>43.3</v>
+        <v>40.4</v>
       </c>
       <c r="K167" s="24" t="n">
-        <v>4623</v>
+        <v>4314</v>
       </c>
       <c r="L167" s="25" t="n">
-        <v>2.9</v>
+        <v>5.8</v>
       </c>
       <c r="M167" s="25" t="n">
-        <v>309</v>
+        <v>618</v>
       </c>
       <c r="N167" s="26" t="n">
         <v>26.7</v>
@@ -33869,16 +33869,16 @@
         <v>20025</v>
       </c>
       <c r="J168" s="24" t="n">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K168" s="24" t="n">
-        <v>2099</v>
+        <v>2012</v>
       </c>
       <c r="L168" s="25" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M168" s="25" t="n">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="N168" s="26" t="n">
         <v>8.4</v>
@@ -34031,16 +34031,16 @@
         <v>6250</v>
       </c>
       <c r="J171" s="24" t="n">
-        <v>62.2</v>
+        <v>61.4</v>
       </c>
       <c r="K171" s="24" t="n">
-        <v>23552</v>
+        <v>23255</v>
       </c>
       <c r="L171" s="25" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="M171" s="25" t="n">
-        <v>3274</v>
+        <v>3572</v>
       </c>
       <c r="N171" s="26" t="n">
         <v>12.6</v>
@@ -34193,16 +34193,16 @@
         <v>25173</v>
       </c>
       <c r="J174" s="24" t="n">
-        <v>34.8</v>
+        <v>34.5</v>
       </c>
       <c r="K174" s="24" t="n">
-        <v>17431</v>
+        <v>17270</v>
       </c>
       <c r="L174" s="25" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="M174" s="25" t="n">
-        <v>322</v>
+        <v>483</v>
       </c>
       <c r="N174" s="26" t="n">
         <v>14.3</v>
@@ -34355,16 +34355,16 @@
         <v>26089</v>
       </c>
       <c r="J177" s="24" t="n">
-        <v>25.2</v>
+        <v>24.7</v>
       </c>
       <c r="K177" s="24" t="n">
-        <v>10750</v>
+        <v>10511</v>
       </c>
       <c r="L177" s="25" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="M177" s="25" t="n">
-        <v>1553</v>
+        <v>1792</v>
       </c>
       <c r="N177" s="26" t="n">
         <v>9.9</v>
@@ -34571,16 +34571,16 @@
         <v>20795</v>
       </c>
       <c r="J181" s="24" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="K181" s="24" t="n">
-        <v>8383</v>
+        <v>8274</v>
       </c>
       <c r="L181" s="25" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="M181" s="25" t="n">
-        <v>544</v>
+        <v>653</v>
       </c>
       <c r="N181" s="26" t="n">
         <v>13.6</v>
@@ -35975,16 +35975,16 @@
         <v>8851</v>
       </c>
       <c r="J207" s="24" t="n">
-        <v>17.1</v>
+        <v>16.2</v>
       </c>
       <c r="K207" s="24" t="n">
-        <v>2385</v>
+        <v>2260</v>
       </c>
       <c r="L207" s="25" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="M207" s="25" t="n">
-        <v>126</v>
+        <v>251</v>
       </c>
       <c r="N207" s="26" t="n">
         <v>18.5</v>
@@ -36000,7 +36000,7 @@
       </c>
       <c r="R207" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -36677,16 +36677,16 @@
         <v>41015</v>
       </c>
       <c r="J220" s="24" t="n">
-        <v>21.5</v>
+        <v>20.6</v>
       </c>
       <c r="K220" s="24" t="n">
-        <v>15442</v>
+        <v>14828</v>
       </c>
       <c r="L220" s="25" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="M220" s="25" t="n">
-        <v>621</v>
+        <v>1235</v>
       </c>
       <c r="N220" s="26" t="n">
         <v>20.6</v>
@@ -37811,16 +37811,16 @@
         <v>71896</v>
       </c>
       <c r="J241" s="24" t="n">
-        <v>27.4</v>
+        <v>27</v>
       </c>
       <c r="K241" s="24" t="n">
-        <v>35638</v>
+        <v>35139</v>
       </c>
       <c r="L241" s="25" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="M241" s="25" t="n">
-        <v>1495</v>
+        <v>1993</v>
       </c>
       <c r="N241" s="26" t="n">
         <v>16.1</v>
@@ -38081,16 +38081,16 @@
         <v>14379</v>
       </c>
       <c r="J246" s="24" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="K246" s="24" t="n">
-        <v>1657</v>
+        <v>1502</v>
       </c>
       <c r="L246" s="25" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="M246" s="25" t="n">
-        <v>1010</v>
+        <v>1166</v>
       </c>
       <c r="N246" s="26" t="n">
         <v>15.8</v>
@@ -38135,16 +38135,16 @@
         <v>4612</v>
       </c>
       <c r="J247" s="24" t="n">
-        <v>22</v>
+        <v>21.6</v>
       </c>
       <c r="K247" s="24" t="n">
-        <v>1600</v>
+        <v>1569</v>
       </c>
       <c r="L247" s="25" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="M247" s="25" t="n">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="N247" s="26" t="n">
         <v>12.4</v>
@@ -38189,16 +38189,16 @@
         <v>16443</v>
       </c>
       <c r="J248" s="24" t="n">
-        <v>18.6</v>
+        <v>17.4</v>
       </c>
       <c r="K248" s="24" t="n">
-        <v>5103</v>
+        <v>4763</v>
       </c>
       <c r="L248" s="25" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="M248" s="25" t="n">
-        <v>1474</v>
+        <v>1814</v>
       </c>
       <c r="N248" s="26" t="n">
         <v>16.1</v>
@@ -38729,16 +38729,16 @@
         <v>32497</v>
       </c>
       <c r="J258" s="24" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="K258" s="24" t="n">
-        <v>5209</v>
+        <v>5021</v>
       </c>
       <c r="L258" s="25" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="M258" s="25" t="n">
-        <v>214</v>
+        <v>402</v>
       </c>
       <c r="N258" s="26" t="n">
         <v>19.3</v>
@@ -38754,7 +38754,7 @@
       </c>
       <c r="R258" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -39053,16 +39053,16 @@
         <v>27642</v>
       </c>
       <c r="J264" s="24" t="n">
-        <v>22.3</v>
+        <v>21.9</v>
       </c>
       <c r="K264" s="24" t="n">
-        <v>10501</v>
+        <v>10288</v>
       </c>
       <c r="L264" s="25" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="M264" s="25" t="n">
-        <v>1699</v>
+        <v>1912</v>
       </c>
       <c r="N264" s="26" t="n">
         <v>15.3</v>
@@ -39215,16 +39215,16 @@
         <v>18125</v>
       </c>
       <c r="J267" s="24" t="n">
-        <v>38.9</v>
+        <v>37.5</v>
       </c>
       <c r="K267" s="24" t="n">
-        <v>26181</v>
+        <v>25294</v>
       </c>
       <c r="L267" s="25" t="n">
-        <v>15</v>
+        <v>16.3</v>
       </c>
       <c r="M267" s="25" t="n">
-        <v>10121</v>
+        <v>11008</v>
       </c>
       <c r="N267" s="26" t="n">
         <v>19.2</v>
@@ -39485,16 +39485,16 @@
         <v>54177</v>
       </c>
       <c r="J272" s="24" t="n">
-        <v>21.9</v>
+        <v>21.5</v>
       </c>
       <c r="K272" s="24" t="n">
-        <v>19566</v>
+        <v>19158</v>
       </c>
       <c r="L272" s="25" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="M272" s="25" t="n">
-        <v>5295</v>
+        <v>5702</v>
       </c>
       <c r="N272" s="26" t="n">
         <v>11.4</v>
@@ -39701,16 +39701,16 @@
         <v>22057</v>
       </c>
       <c r="J276" s="24" t="n">
-        <v>39.2</v>
+        <v>38.7</v>
       </c>
       <c r="K276" s="24" t="n">
-        <v>19757</v>
+        <v>19508</v>
       </c>
       <c r="L276" s="25" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="M276" s="25" t="n">
-        <v>1871</v>
+        <v>2120</v>
       </c>
       <c r="N276" s="26" t="n">
         <v>13.4</v>
@@ -39863,16 +39863,16 @@
         <v>20787</v>
       </c>
       <c r="J279" s="24" t="n">
-        <v>31.4</v>
+        <v>29.7</v>
       </c>
       <c r="K279" s="24" t="n">
-        <v>12314</v>
+        <v>11649</v>
       </c>
       <c r="L279" s="25" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="M279" s="25" t="n">
-        <v>166</v>
+        <v>831</v>
       </c>
       <c r="N279" s="26" t="n">
         <v>15.3</v>
@@ -40619,16 +40619,16 @@
         <v>8196</v>
       </c>
       <c r="J293" s="24" t="n">
-        <v>23.7</v>
+        <v>22.4</v>
       </c>
       <c r="K293" s="24" t="n">
-        <v>3342</v>
+        <v>3158</v>
       </c>
       <c r="L293" s="25" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="M293" s="25" t="n">
-        <v>583</v>
+        <v>767</v>
       </c>
       <c r="N293" s="26" t="n">
         <v>13.9</v>
@@ -40727,16 +40727,16 @@
         <v>12037</v>
       </c>
       <c r="J295" s="24" t="n">
-        <v>47.5</v>
+        <v>29.1</v>
       </c>
       <c r="K295" s="24" t="n">
-        <v>15560</v>
+        <v>9542</v>
       </c>
       <c r="L295" s="25" t="n">
-        <v>8.1</v>
+        <v>26.5</v>
       </c>
       <c r="M295" s="25" t="n">
-        <v>2642</v>
+        <v>8661</v>
       </c>
       <c r="N295" s="26" t="n">
         <v>7.6</v>
@@ -40752,7 +40752,7 @@
       </c>
       <c r="R295" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -40781,16 +40781,16 @@
         <v>2634</v>
       </c>
       <c r="J296" s="24" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K296" s="24" t="n">
-        <v>7727</v>
+        <v>7610</v>
       </c>
       <c r="L296" s="25" t="n">
-        <v>10.3</v>
+        <v>11.3</v>
       </c>
       <c r="M296" s="25" t="n">
-        <v>1288</v>
+        <v>1405</v>
       </c>
       <c r="N296" s="26" t="n">
         <v>6.6</v>
@@ -40835,16 +40835,16 @@
         <v>5565</v>
       </c>
       <c r="J297" s="24" t="n">
-        <v>64</v>
+        <v>63.2</v>
       </c>
       <c r="K297" s="24" t="n">
-        <v>14810</v>
+        <v>14631</v>
       </c>
       <c r="L297" s="25" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="M297" s="25" t="n">
-        <v>449</v>
+        <v>628</v>
       </c>
       <c r="N297" s="26" t="n">
         <v>10.1</v>
@@ -40943,16 +40943,16 @@
         <v>2488</v>
       </c>
       <c r="J299" s="24" t="n">
-        <v>69.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K299" s="24" t="n">
-        <v>10074</v>
+        <v>10024</v>
       </c>
       <c r="L299" s="25" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="M299" s="25" t="n">
-        <v>109</v>
+        <v>160</v>
       </c>
       <c r="N299" s="26" t="n">
         <v>12.7</v>
@@ -41051,16 +41051,16 @@
         <v>679</v>
       </c>
       <c r="J301" s="24" t="n">
-        <v>72.90000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K301" s="24" t="n">
-        <v>7317</v>
+        <v>7138</v>
       </c>
       <c r="L301" s="25" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="M301" s="25" t="n">
-        <v>412</v>
+        <v>591</v>
       </c>
       <c r="N301" s="26" t="n">
         <v>16.2</v>
@@ -41105,16 +41105,16 @@
         <v>3089</v>
       </c>
       <c r="J302" s="24" t="n">
-        <v>63.6</v>
+        <v>62.1</v>
       </c>
       <c r="K302" s="24" t="n">
-        <v>14332</v>
+        <v>13989</v>
       </c>
       <c r="L302" s="25" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="M302" s="25" t="n">
-        <v>840</v>
+        <v>1183</v>
       </c>
       <c r="N302" s="26" t="n">
         <v>19</v>
@@ -41321,16 +41321,16 @@
         <v>1414</v>
       </c>
       <c r="J306" s="24" t="n">
-        <v>69.7</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K306" s="24" t="n">
-        <v>7726</v>
+        <v>7544</v>
       </c>
       <c r="L306" s="25" t="n">
-        <v>6.4</v>
+        <v>8.1</v>
       </c>
       <c r="M306" s="25" t="n">
-        <v>713</v>
+        <v>895</v>
       </c>
       <c r="N306" s="26" t="n">
         <v>11.1</v>
@@ -41483,16 +41483,16 @@
         <v>25190</v>
       </c>
       <c r="J309" s="24" t="n">
-        <v>32.8</v>
+        <v>14.7</v>
       </c>
       <c r="K309" s="24" t="n">
-        <v>13987</v>
+        <v>6270</v>
       </c>
       <c r="L309" s="25" t="n">
-        <v>1.6</v>
+        <v>19.7</v>
       </c>
       <c r="M309" s="25" t="n">
-        <v>697</v>
+        <v>8414</v>
       </c>
       <c r="N309" s="26" t="n">
         <v>6.6</v>
@@ -41508,7 +41508,7 @@
       </c>
       <c r="R309" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -41537,16 +41537,16 @@
         <v>13893</v>
       </c>
       <c r="J310" s="24" t="n">
-        <v>41.7</v>
+        <v>38.1</v>
       </c>
       <c r="K310" s="24" t="n">
-        <v>15047</v>
+        <v>13750</v>
       </c>
       <c r="L310" s="25" t="n">
-        <v>2.3</v>
+        <v>5.9</v>
       </c>
       <c r="M310" s="25" t="n">
-        <v>825</v>
+        <v>2122</v>
       </c>
       <c r="N310" s="26" t="n">
         <v>17.5</v>
@@ -41562,7 +41562,7 @@
       </c>
       <c r="R310" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -41591,16 +41591,16 @@
         <v>8095</v>
       </c>
       <c r="J311" s="24" t="n">
-        <v>49</v>
+        <v>41.7</v>
       </c>
       <c r="K311" s="24" t="n">
-        <v>12026</v>
+        <v>10251</v>
       </c>
       <c r="L311" s="25" t="n">
-        <v>1.7</v>
+        <v>8.9</v>
       </c>
       <c r="M311" s="25" t="n">
-        <v>418</v>
+        <v>2193</v>
       </c>
       <c r="N311" s="26" t="n">
         <v>16.4</v>
@@ -41616,7 +41616,7 @@
       </c>
       <c r="R311" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -41645,16 +41645,16 @@
         <v>7608</v>
       </c>
       <c r="J312" s="24" t="n">
-        <v>65.90000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="K312" s="24" t="n">
-        <v>27166</v>
+        <v>25590</v>
       </c>
       <c r="L312" s="25" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="M312" s="25" t="n">
-        <v>591</v>
+        <v>2168</v>
       </c>
       <c r="N312" s="26" t="n">
         <v>14.2</v>
@@ -41699,16 +41699,16 @@
         <v>11095</v>
       </c>
       <c r="J313" s="24" t="n">
-        <v>52.4</v>
+        <v>46.8</v>
       </c>
       <c r="K313" s="24" t="n">
-        <v>25565</v>
+        <v>22847</v>
       </c>
       <c r="L313" s="25" t="n">
-        <v>0.9</v>
+        <v>6.4</v>
       </c>
       <c r="M313" s="25" t="n">
-        <v>418</v>
+        <v>3136</v>
       </c>
       <c r="N313" s="26" t="n">
         <v>24</v>
@@ -41753,16 +41753,16 @@
         <v>11178</v>
       </c>
       <c r="J314" s="24" t="n">
-        <v>56.7</v>
+        <v>48</v>
       </c>
       <c r="K314" s="24" t="n">
-        <v>26766</v>
+        <v>22652</v>
       </c>
       <c r="L314" s="25" t="n">
-        <v>3.3</v>
+        <v>12</v>
       </c>
       <c r="M314" s="25" t="n">
-        <v>1543</v>
+        <v>5657</v>
       </c>
       <c r="N314" s="26" t="n">
         <v>16.4</v>
@@ -41778,7 +41778,7 @@
       </c>
       <c r="R314" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -41807,16 +41807,16 @@
         <v>3202</v>
       </c>
       <c r="J315" s="24" t="n">
-        <v>63.4</v>
+        <v>56.6</v>
       </c>
       <c r="K315" s="24" t="n">
-        <v>12474</v>
+        <v>11140</v>
       </c>
       <c r="L315" s="25" t="n">
-        <v>4.1</v>
+        <v>10.8</v>
       </c>
       <c r="M315" s="25" t="n">
-        <v>800</v>
+        <v>2135</v>
       </c>
       <c r="N315" s="26" t="n">
         <v>16.3</v>
@@ -41861,16 +41861,16 @@
         <v>4286</v>
       </c>
       <c r="J316" s="24" t="n">
-        <v>66</v>
+        <v>62.7</v>
       </c>
       <c r="K316" s="24" t="n">
-        <v>15507</v>
+        <v>14715</v>
       </c>
       <c r="L316" s="25" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="M316" s="25" t="n">
-        <v>238</v>
+        <v>1029</v>
       </c>
       <c r="N316" s="26" t="n">
         <v>14.7</v>
@@ -41969,16 +41969,16 @@
         <v>13543</v>
       </c>
       <c r="J318" s="24" t="n">
-        <v>56.6</v>
+        <v>48.7</v>
       </c>
       <c r="K318" s="24" t="n">
-        <v>26245</v>
+        <v>22569</v>
       </c>
       <c r="L318" s="25" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M318" s="25" t="n">
-        <v>479</v>
+        <v>4155</v>
       </c>
       <c r="N318" s="26" t="n">
         <v>13.1</v>
@@ -41994,7 +41994,7 @@
       </c>
       <c r="R318" s="28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -42077,16 +42077,16 @@
         <v>2822</v>
       </c>
       <c r="J320" s="24" t="n">
-        <v>56.5</v>
+        <v>53.6</v>
       </c>
       <c r="K320" s="24" t="n">
-        <v>5861</v>
+        <v>5557</v>
       </c>
       <c r="L320" s="25" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="M320" s="25" t="n">
-        <v>43</v>
+        <v>347</v>
       </c>
       <c r="N320" s="26" t="n">
         <v>15.9</v>
@@ -42131,16 +42131,16 @@
         <v>500</v>
       </c>
       <c r="J321" s="24" t="n">
-        <v>82.8</v>
+        <v>77.3</v>
       </c>
       <c r="K321" s="24" t="n">
-        <v>9023</v>
+        <v>8423</v>
       </c>
       <c r="L321" s="25" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="M321" s="25" t="n">
-        <v>250</v>
+        <v>850</v>
       </c>
       <c r="N321" s="26" t="n">
         <v>10.4</v>
@@ -42185,16 +42185,16 @@
         <v>1487</v>
       </c>
       <c r="J322" s="24" t="n">
-        <v>46.4</v>
+        <v>44.2</v>
       </c>
       <c r="K322" s="24" t="n">
-        <v>2188</v>
+        <v>2086</v>
       </c>
       <c r="L322" s="25" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="M322" s="25" t="n">
-        <v>68</v>
+        <v>171</v>
       </c>
       <c r="N322" s="26" t="n">
         <v>20.7</v>
@@ -42239,16 +42239,16 @@
         <v>5755</v>
       </c>
       <c r="J323" s="24" t="n">
-        <v>53</v>
+        <v>51.9</v>
       </c>
       <c r="K323" s="24" t="n">
-        <v>15621</v>
+        <v>15313</v>
       </c>
       <c r="L323" s="25" t="n">
-        <v>6.6</v>
+        <v>7.7</v>
       </c>
       <c r="M323" s="25" t="n">
-        <v>1953</v>
+        <v>2261</v>
       </c>
       <c r="N323" s="26" t="n">
         <v>20.9</v>
@@ -42293,16 +42293,16 @@
         <v>484</v>
       </c>
       <c r="J324" s="24" t="n">
-        <v>53.5</v>
+        <v>52.8</v>
       </c>
       <c r="K324" s="24" t="n">
-        <v>1322</v>
+        <v>1305</v>
       </c>
       <c r="L324" s="25" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="M324" s="25" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="N324" s="26" t="n">
         <v>25.2</v>
@@ -42455,16 +42455,16 @@
         <v>7707</v>
       </c>
       <c r="J327" s="24" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="K327" s="24" t="n">
-        <v>2528</v>
+        <v>2491</v>
       </c>
       <c r="L327" s="25" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="M327" s="25" t="n">
-        <v>375</v>
+        <v>412</v>
       </c>
       <c r="N327" s="26" t="n">
         <v>18.3</v>
@@ -42617,16 +42617,16 @@
         <v>3275</v>
       </c>
       <c r="J330" s="24" t="n">
-        <v>16.3</v>
+        <v>16</v>
       </c>
       <c r="K330" s="24" t="n">
-        <v>807</v>
+        <v>790</v>
       </c>
       <c r="L330" s="25" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="M330" s="25" t="n">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="N330" s="26" t="n">
         <v>14.4</v>
@@ -42833,16 +42833,16 @@
         <v>8327</v>
       </c>
       <c r="J334" s="24" t="n">
-        <v>16.1</v>
+        <v>15.3</v>
       </c>
       <c r="K334" s="24" t="n">
-        <v>2021</v>
+        <v>1917</v>
       </c>
       <c r="L334" s="25" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="M334" s="25" t="n">
-        <v>259</v>
+        <v>363</v>
       </c>
       <c r="N334" s="26" t="n">
         <v>15.5</v>
@@ -42887,16 +42887,16 @@
         <v>14692</v>
       </c>
       <c r="J335" s="24" t="n">
-        <v>22.9</v>
+        <v>22.5</v>
       </c>
       <c r="K335" s="24" t="n">
-        <v>6090</v>
+        <v>5997</v>
       </c>
       <c r="L335" s="25" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="M335" s="25" t="n">
-        <v>480</v>
+        <v>573</v>
       </c>
       <c r="N335" s="26" t="n">
         <v>20.2</v>
@@ -43697,16 +43697,16 @@
         <v>34038</v>
       </c>
       <c r="J350" s="24" t="n">
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="K350" s="24" t="n">
-        <v>8126</v>
+        <v>7805</v>
       </c>
       <c r="L350" s="25" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="M350" s="25" t="n">
-        <v>976</v>
+        <v>1297</v>
       </c>
       <c r="N350" s="26" t="n">
         <v>17</v>
@@ -43751,16 +43751,16 @@
         <v>59531</v>
       </c>
       <c r="J351" s="24" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="K351" s="24" t="n">
-        <v>62159</v>
+        <v>61614</v>
       </c>
       <c r="L351" s="25" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="M351" s="25" t="n">
-        <v>1639</v>
+        <v>2183</v>
       </c>
       <c r="N351" s="26" t="n">
         <v>17.2</v>
@@ -43967,16 +43967,16 @@
         <v>35205</v>
       </c>
       <c r="J355" s="24" t="n">
-        <v>38.2</v>
+        <v>37.9</v>
       </c>
       <c r="K355" s="24" t="n">
-        <v>35212</v>
+        <v>34921</v>
       </c>
       <c r="L355" s="25" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="M355" s="25" t="n">
-        <v>5234</v>
+        <v>5525</v>
       </c>
       <c r="N355" s="26" t="n">
         <v>18</v>
@@ -44291,16 +44291,16 @@
         <v>14412</v>
       </c>
       <c r="J361" s="24" t="n">
-        <v>61.1</v>
+        <v>60.9</v>
       </c>
       <c r="K361" s="24" t="n">
-        <v>43479</v>
+        <v>43279</v>
       </c>
       <c r="L361" s="25" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="M361" s="25" t="n">
-        <v>2202</v>
+        <v>2402</v>
       </c>
       <c r="N361" s="26" t="n">
         <v>15.5</v>
@@ -44399,16 +44399,16 @@
         <v>19795</v>
       </c>
       <c r="J363" s="24" t="n">
-        <v>26.6</v>
+        <v>25.8</v>
       </c>
       <c r="K363" s="24" t="n">
-        <v>8058</v>
+        <v>7814</v>
       </c>
       <c r="L363" s="25" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M363" s="25" t="n">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="N363" s="26" t="n">
         <v>8.1</v>
@@ -44507,16 +44507,16 @@
         <v>1091</v>
       </c>
       <c r="J365" s="24" t="n">
-        <v>76.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K365" s="24" t="n">
-        <v>11636</v>
+        <v>11591</v>
       </c>
       <c r="L365" s="25" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="M365" s="25" t="n">
-        <v>364</v>
+        <v>409</v>
       </c>
       <c r="N365" s="26" t="n">
         <v>13.5</v>
@@ -44831,16 +44831,16 @@
         <v>38689</v>
       </c>
       <c r="J371" s="24" t="n">
-        <v>17</v>
+        <v>16.1</v>
       </c>
       <c r="K371" s="24" t="n">
-        <v>11249</v>
+        <v>10684</v>
       </c>
       <c r="L371" s="25" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="M371" s="25" t="n">
-        <v>3918</v>
+        <v>4483</v>
       </c>
       <c r="N371" s="26" t="n">
         <v>18.7</v>
@@ -44885,16 +44885,16 @@
         <v>63100</v>
       </c>
       <c r="J372" s="24" t="n">
-        <v>25</v>
+        <v>24.6</v>
       </c>
       <c r="K372" s="24" t="n">
-        <v>25849</v>
+        <v>25450</v>
       </c>
       <c r="L372" s="25" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="M372" s="25" t="n">
-        <v>2396</v>
+        <v>2796</v>
       </c>
       <c r="N372" s="26" t="n">
         <v>11.7</v>
@@ -45533,16 +45533,16 @@
         <v>6673</v>
       </c>
       <c r="J384" s="24" t="n">
-        <v>52.4</v>
+        <v>49.2</v>
       </c>
       <c r="K384" s="24" t="n">
-        <v>10322</v>
+        <v>9697</v>
       </c>
       <c r="L384" s="25" t="n">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="M384" s="25" t="n">
-        <v>417</v>
+        <v>1042</v>
       </c>
       <c r="N384" s="26" t="n">
         <v>11.6</v>
@@ -45749,16 +45749,16 @@
         <v>459</v>
       </c>
       <c r="J388" s="24" t="n">
-        <v>64.09999999999999</v>
+        <v>63.7</v>
       </c>
       <c r="K388" s="24" t="n">
-        <v>11356</v>
+        <v>11280</v>
       </c>
       <c r="L388" s="25" t="n">
-        <v>18.4</v>
+        <v>18.8</v>
       </c>
       <c r="M388" s="25" t="n">
-        <v>3252</v>
+        <v>3328</v>
       </c>
       <c r="N388" s="26" t="n">
         <v>14.9</v>
@@ -45803,16 +45803,16 @@
         <v>6042</v>
       </c>
       <c r="J389" s="24" t="n">
-        <v>32.3</v>
+        <v>30.8</v>
       </c>
       <c r="K389" s="24" t="n">
-        <v>4296</v>
+        <v>4107</v>
       </c>
       <c r="L389" s="25" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="M389" s="25" t="n">
-        <v>1008</v>
+        <v>1196</v>
       </c>
       <c r="N389" s="26" t="n">
         <v>14.8</v>
@@ -45911,16 +45911,16 @@
         <v>7475</v>
       </c>
       <c r="J391" s="24" t="n">
-        <v>60.4</v>
+        <v>59.2</v>
       </c>
       <c r="K391" s="24" t="n">
-        <v>23553</v>
+        <v>23076</v>
       </c>
       <c r="L391" s="25" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="M391" s="25" t="n">
-        <v>2636</v>
+        <v>3113</v>
       </c>
       <c r="N391" s="26" t="n">
         <v>13.6</v>
@@ -45965,16 +45965,16 @@
         <v>8216</v>
       </c>
       <c r="J392" s="24" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="K392" s="24" t="n">
-        <v>847</v>
+        <v>805</v>
       </c>
       <c r="L392" s="25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="M392" s="25" t="n">
-        <v>974</v>
+        <v>1016</v>
       </c>
       <c r="N392" s="26" t="n">
         <v>15.1</v>
@@ -46127,16 +46127,16 @@
         <v>0</v>
       </c>
       <c r="J395" s="24" t="n">
-        <v>75.5</v>
+        <v>65</v>
       </c>
       <c r="K395" s="24" t="n">
-        <v>21968</v>
+        <v>18901</v>
       </c>
       <c r="L395" s="25" t="n">
-        <v>6.1</v>
+        <v>16.7</v>
       </c>
       <c r="M395" s="25" t="n">
-        <v>1781</v>
+        <v>4849</v>
       </c>
       <c r="N395" s="26" t="n">
         <v>18.4</v>
@@ -46181,16 +46181,16 @@
         <v>14824</v>
       </c>
       <c r="J396" s="24" t="n">
-        <v>38.3</v>
+        <v>37.9</v>
       </c>
       <c r="K396" s="24" t="n">
-        <v>15089</v>
+        <v>14957</v>
       </c>
       <c r="L396" s="25" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="M396" s="25" t="n">
-        <v>1324</v>
+        <v>1456</v>
       </c>
       <c r="N396" s="26" t="n">
         <v>20.8</v>
@@ -46499,7 +46499,7 @@
   <cols>
     <col width="35" customWidth="1" min="5" max="5"/>
     <col width="90" customWidth="1" min="6" max="6"/>
-    <col width="288" customWidth="1" min="7" max="7"/>
+    <col width="340" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -46571,7 +46571,7 @@
       </c>
       <c r="G7" s="35" t="inlineStr">
         <is>
-          <t>25/09/2025 10:20</t>
+          <t>25/09/2025 10:27</t>
         </is>
       </c>
     </row>
@@ -46823,7 +46823,7 @@
       </c>
       <c r="G19" s="35" t="inlineStr">
         <is>
-          <t>['Well-being during travel or at school', "Child needs to work at home or on the household's own farm (i.e. is not earning an income for these activities, but may allow other family members to earn an income) ", 'Child participating in income generating activities outside of the home']</t>
+          <t>['Well-being during travel or at school', "Child needs to work at home or on the household's own farm (i.e. is not earning an income for these activities, but may allow other family members to earn an income) ", 'Child participating in income generating activities outside of the home', 'Personal or family responsibilities (for female)']</t>
         </is>
       </c>
     </row>
